--- a/docs/d/47/inyear.xlsx
+++ b/docs/d/47/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 75 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 72 clubs short</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" s="9" t="n">
         <v>0</v>
@@ -2528,8 +2528,8 @@
       <c r="S18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T18" s="9" t="n">
-        <v>0</v>
+      <c r="T18" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U18" s="9" t="n">
         <v>0</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3051,8 +3051,8 @@
       <c r="Y23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z23" s="9" t="n">
-        <v>0</v>
+      <c r="Z23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA23" s="10" t="n">
         <v>1</v>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="P31" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q31" s="9" t="n">
         <v>0</v>
@@ -7572,7 +7572,7 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7586,13 +7586,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7642,8 +7642,8 @@
       <c r="Y68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z68" s="9" t="n">
-        <v>0</v>
+      <c r="Z68" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA68" s="10" t="n">
         <v>1</v>
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10502,8 +10502,8 @@
       <c r="S96" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T96" s="9" t="n">
-        <v>0</v>
+      <c r="T96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U96" s="9" t="n">
         <v>0</v>
@@ -12304,7 +12304,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12353,11 +12353,11 @@
       <c r="R114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S114" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T114" s="9" t="n">
-        <v>0</v>
+      <c r="S114" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T114" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U114" s="9" t="n">
         <v>0</v>
@@ -14278,7 +14278,7 @@
         </is>
       </c>
       <c r="P133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q133" s="9" t="n">
         <v>1</v>
@@ -16600,7 +16600,7 @@
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -16643,8 +16643,8 @@
       <c r="P156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" s="9" t="n">
-        <v>0</v>
+      <c r="Q156" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R156" s="9" t="n">
         <v>0</v>
@@ -17418,7 +17418,7 @@
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F164" s="6" t="n">
         <v>10</v>
@@ -17467,8 +17467,8 @@
       <c r="R164" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S164" s="9" t="n">
-        <v>1</v>
+      <c r="S164" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T164" s="10" t="n">
         <v>1</v>
@@ -18012,7 +18012,7 @@
         </is>
       </c>
       <c r="E170" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F170" s="6" t="n">
         <v>10</v>
@@ -18082,8 +18082,8 @@
       <c r="Y170" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z170" s="9" t="n">
-        <v>0</v>
+      <c r="Z170" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA170" s="10" t="n">
         <v>1</v>
@@ -19664,7 +19664,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -19697,7 +19697,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -19994,7 +19994,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -20159,7 +20159,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -20522,7 +20522,7 @@
         <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -20588,7 +20588,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -20621,7 +20621,7 @@
         <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>

--- a/docs/d/47/inyear.xlsx
+++ b/docs/d/47/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,11 @@
       <c r="AB8" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC8" s="4" t="inlineStr"/>
+      <c r="AC8" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1642,7 +1646,11 @@
       <c r="AB9" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC9" s="4" t="inlineStr"/>
+      <c r="AC9" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -2858,7 +2866,11 @@
       <c r="AB21" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC21" s="4" t="inlineStr"/>
+      <c r="AC21" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -2959,7 +2971,11 @@
       <c r="AB22" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC22" s="4" t="inlineStr"/>
+      <c r="AC22" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -3165,7 +3181,11 @@
       <c r="AB24" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC24" s="4" t="inlineStr"/>
+      <c r="AC24" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -3371,7 +3391,11 @@
       <c r="AB26" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC26" s="4" t="inlineStr"/>
+      <c r="AC26" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -3472,7 +3496,11 @@
       <c r="AB27" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC27" s="4" t="inlineStr"/>
+      <c r="AC27" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -3880,7 +3908,11 @@
       <c r="AB31" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC31" s="4" t="inlineStr"/>
+      <c r="AC31" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -4694,7 +4726,11 @@
       <c r="AB39" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC39" s="4" t="inlineStr"/>
+      <c r="AC39" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -5001,7 +5037,11 @@
       <c r="AB42" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC42" s="4" t="inlineStr"/>
+      <c r="AC42" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -5203,7 +5243,11 @@
       <c r="AB44" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC44" s="4" t="inlineStr"/>
+      <c r="AC44" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -5809,7 +5853,11 @@
       <c r="AB50" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC50" s="4" t="inlineStr"/>
+      <c r="AC50" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -5910,7 +5958,11 @@
       <c r="AB51" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC51" s="4" t="inlineStr"/>
+      <c r="AC51" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -6112,7 +6164,11 @@
       <c r="AB53" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC53" s="4" t="inlineStr"/>
+      <c r="AC53" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -6629,7 +6685,11 @@
       <c r="AB58" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC58" s="4" t="inlineStr"/>
+      <c r="AC58" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -6730,7 +6790,11 @@
       <c r="AB59" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC59" s="4" t="inlineStr"/>
+      <c r="AC59" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -6831,7 +6895,11 @@
       <c r="AB60" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC60" s="4" t="inlineStr"/>
+      <c r="AC60" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -7033,7 +7101,11 @@
       <c r="AB62" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC62" s="4" t="inlineStr"/>
+      <c r="AC62" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -8582,7 +8654,11 @@
       <c r="AB77" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC77" s="4" t="inlineStr"/>
+      <c r="AC77" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -8683,7 +8759,11 @@
       <c r="AB78" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC78" s="4" t="inlineStr"/>
+      <c r="AC78" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -8784,7 +8864,11 @@
       <c r="AB79" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC79" s="4" t="inlineStr"/>
+      <c r="AC79" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -9406,7 +9490,11 @@
       <c r="AB85" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC85" s="4" t="inlineStr"/>
+      <c r="AC85" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -9915,7 +10003,11 @@
       <c r="AB90" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC90" s="4" t="inlineStr"/>
+      <c r="AC90" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -10949,7 +11041,11 @@
       <c r="AB100" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC100" s="4" t="inlineStr"/>
+      <c r="AC100" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -11155,7 +11251,11 @@
       <c r="AB102" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC102" s="4" t="inlineStr"/>
+      <c r="AC102" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -11571,7 +11671,11 @@
       <c r="AB106" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC106" s="4" t="inlineStr"/>
+      <c r="AC106" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -12383,7 +12487,11 @@
       <c r="AB114" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC114" s="4" t="inlineStr"/>
+      <c r="AC114" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -12484,7 +12592,11 @@
       <c r="AB115" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC115" s="4" t="inlineStr"/>
+      <c r="AC115" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -13405,7 +13517,11 @@
       <c r="AB124" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC124" s="4" t="inlineStr"/>
+      <c r="AC124" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -13811,7 +13927,11 @@
       <c r="AB128" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC128" s="4" t="inlineStr"/>
+      <c r="AC128" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -14013,7 +14133,11 @@
       <c r="AB130" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC130" s="4" t="inlineStr"/>
+      <c r="AC130" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -14114,7 +14238,11 @@
       <c r="AB131" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC131" s="4" t="inlineStr"/>
+      <c r="AC131" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -14215,7 +14343,11 @@
       <c r="AB132" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC132" s="4" t="inlineStr"/>
+      <c r="AC132" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -14316,7 +14448,11 @@
       <c r="AB133" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC133" s="4" t="inlineStr"/>
+      <c r="AC133" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -14417,7 +14553,11 @@
       <c r="AB134" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC134" s="4" t="inlineStr"/>
+      <c r="AC134" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -15342,7 +15482,11 @@
       <c r="AB143" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC143" s="4" t="inlineStr"/>
+      <c r="AC143" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
@@ -15855,7 +15999,11 @@
       <c r="AB148" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC148" s="4" t="inlineStr"/>
+      <c r="AC148" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
@@ -16061,7 +16209,11 @@
       <c r="AB150" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC150" s="4" t="inlineStr"/>
+      <c r="AC150" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
@@ -16162,7 +16314,11 @@
       <c r="AB151" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC151" s="4" t="inlineStr"/>
+      <c r="AC151" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
@@ -16784,7 +16940,11 @@
       <c r="AB157" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC157" s="4" t="inlineStr"/>
+      <c r="AC157" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
@@ -16885,7 +17045,11 @@
       <c r="AB158" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC158" s="4" t="inlineStr"/>
+      <c r="AC158" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
@@ -16986,7 +17150,11 @@
       <c r="AB159" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC159" s="4" t="inlineStr"/>
+      <c r="AC159" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
@@ -17192,7 +17360,11 @@
       <c r="AB161" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC161" s="4" t="inlineStr"/>
+      <c r="AC161" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">

--- a/docs/d/47/inyear.xlsx
+++ b/docs/d/47/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 21 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 21 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 72 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 66 clubs short</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -1007,11 +1007,11 @@
       <c r="U3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V3" s="9" t="n">
-        <v>3</v>
+      <c r="V3" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" s="10" t="n">
         <v>7</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5541,8 +5541,8 @@
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
@@ -6620,13 +6620,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>4</v>
       </c>
       <c r="W58" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X58" s="10" t="n">
         <v>5</v>
@@ -6857,7 +6857,7 @@
         </is>
       </c>
       <c r="P60" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q60" s="9" t="n">
         <v>1</v>
@@ -7329,7 +7329,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7343,13 +7343,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
@@ -7387,8 +7387,8 @@
       <c r="U65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V65" s="9" t="n">
-        <v>2</v>
+      <c r="V65" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -8212,7 +8212,7 @@
         <v>2</v>
       </c>
       <c r="R73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S73" s="9" t="n">
         <v>0</v>
@@ -8680,7 +8680,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8732,11 +8732,11 @@
       <c r="S78" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T78" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" s="9" t="n">
-        <v>0</v>
+      <c r="T78" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V78" s="10" t="n">
         <v>4</v>
@@ -9411,7 +9411,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9481,8 +9481,8 @@
       <c r="Y85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z85" s="9" t="n">
-        <v>0</v>
+      <c r="Z85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA85" s="10" t="n">
         <v>1</v>
@@ -9617,7 +9617,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9687,8 +9687,8 @@
       <c r="Y87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z87" s="9" t="n">
-        <v>0</v>
+      <c r="Z87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA87" s="10" t="n">
         <v>1</v>
@@ -10586,7 +10586,7 @@
         <v>1</v>
       </c>
       <c r="Q96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R96" s="9" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10927,8 +10927,8 @@
       <c r="Y99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z99" s="9" t="n">
-        <v>0</v>
+      <c r="Z99" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA99" s="10" t="n">
         <v>1</v>
@@ -11277,7 +11277,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11347,8 +11347,8 @@
       <c r="Y103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z103" s="9" t="n">
-        <v>0</v>
+      <c r="Z103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA103" s="10" t="n">
         <v>1</v>
@@ -12000,7 +12000,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -12070,8 +12070,8 @@
       <c r="Y110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z110" s="9" t="n">
-        <v>0</v>
+      <c r="Z110" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA110" s="10" t="n">
         <v>1</v>
@@ -12408,7 +12408,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12463,8 +12463,8 @@
       <c r="T114" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U114" s="9" t="n">
-        <v>0</v>
+      <c r="U114" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V114" s="9" t="n">
         <v>2</v>
@@ -13862,13 +13862,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         </is>
       </c>
       <c r="P128" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q128" s="9" t="n">
         <v>1</v>
@@ -13910,7 +13910,7 @@
         <v>4</v>
       </c>
       <c r="W128" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X128" s="10" t="n">
         <v>7</v>
@@ -14054,7 +14054,7 @@
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -14068,13 +14068,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
@@ -14112,8 +14112,8 @@
       <c r="U130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V130" s="9" t="n">
-        <v>0</v>
+      <c r="V130" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W130" s="9" t="n">
         <v>0</v>
@@ -14474,7 +14474,7 @@
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -14488,13 +14488,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
@@ -14532,11 +14532,11 @@
       <c r="U134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V134" s="9" t="n">
-        <v>0</v>
+      <c r="V134" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W134" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X134" s="10" t="n">
         <v>7</v>
@@ -16861,7 +16861,7 @@
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -16911,13 +16911,13 @@
         <v>1</v>
       </c>
       <c r="S157" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T157" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U157" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="T157" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U157" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V157" s="9" t="n">
         <v>0</v>
@@ -17322,7 +17322,7 @@
         </is>
       </c>
       <c r="P161" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q161" s="10" t="n">
         <v>2</v>
@@ -19737,7 +19737,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -20001,7 +20001,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -20133,7 +20133,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -20232,13 +20232,13 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -20265,7 +20265,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -20331,7 +20331,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -20364,7 +20364,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -20397,7 +20397,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -20430,7 +20430,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -20529,7 +20529,7 @@
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>2.67</v>
+        <v>2.83</v>
       </c>
       <c r="E26" t="n">
         <v>2</v>
@@ -20562,7 +20562,7 @@
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -20694,7 +20694,7 @@
         <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>

--- a/docs/d/47/inyear.xlsx
+++ b/docs/d/47/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 21 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 21 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 66 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 30 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -918,8 +918,8 @@
       <c r="Y2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="9" t="n">
-        <v>0</v>
+      <c r="Z2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA2" s="10" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1225,8 +1225,8 @@
       <c r="Y5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="9" t="n">
-        <v>0</v>
+      <c r="Z5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA5" s="10" t="n">
         <v>1</v>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1326,8 +1326,8 @@
       <c r="Y6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" s="9" t="n">
-        <v>0</v>
+      <c r="Z6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA6" s="10" t="n">
         <v>1</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1616,8 +1616,8 @@
       <c r="R9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" s="9" t="n">
-        <v>1</v>
+      <c r="S9" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T9" s="10" t="n">
         <v>1</v>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1686,13 +1686,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -1721,8 +1721,8 @@
       <c r="R10" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="S10" s="9" t="n">
-        <v>1</v>
+      <c r="S10" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T10" s="9" t="n">
         <v>0</v>
@@ -1734,7 +1734,7 @@
         <v>4</v>
       </c>
       <c r="W10" s="10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X10" s="10" t="n">
         <v>7</v>
@@ -1944,8 +1944,8 @@
       <c r="Y12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" s="9" t="n">
-        <v>0</v>
+      <c r="Z12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA12" s="9" t="n">
         <v>0</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2146,8 +2146,8 @@
       <c r="Y14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="n">
-        <v>0</v>
+      <c r="Z14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="10" t="n">
         <v>1</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2431,8 +2431,8 @@
       <c r="S17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T17" s="9" t="n">
-        <v>0</v>
+      <c r="T17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U17" s="9" t="n">
         <v>0</v>
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="P23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="9" t="n">
         <v>0</v>
@@ -4752,7 +4752,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4822,8 +4822,8 @@
       <c r="Y40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z40" s="9" t="n">
-        <v>0</v>
+      <c r="Z40" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA40" s="10" t="n">
         <v>1</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4927,8 +4927,8 @@
       <c r="Y41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z41" s="9" t="n">
-        <v>0</v>
+      <c r="Z41" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA41" s="10" t="n">
         <v>1</v>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6361,8 +6361,8 @@
       <c r="Y55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z55" s="9" t="n">
-        <v>0</v>
+      <c r="Z55" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA55" s="10" t="n">
         <v>1</v>
@@ -6857,7 +6857,7 @@
         </is>
       </c>
       <c r="P60" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q60" s="9" t="n">
         <v>1</v>
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7298,8 +7298,8 @@
       <c r="Y64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z64" s="9" t="n">
-        <v>0</v>
+      <c r="Z64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA64" s="10" t="n">
         <v>1</v>
@@ -7553,13 +7553,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>1</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -8104,7 +8104,7 @@
         <v>0</v>
       </c>
       <c r="Q72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" s="9" t="n">
         <v>0</v>
@@ -8799,13 +8799,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>4</v>
       </c>
       <c r="W79" s="10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X79" s="10" t="n">
         <v>5</v>
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9170,8 +9170,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -9516,7 +9516,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9581,13 +9581,13 @@
         <v>0</v>
       </c>
       <c r="X86" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z86" s="9" t="n">
-        <v>0</v>
+      <c r="Z86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA86" s="10" t="n">
         <v>1</v>
@@ -9722,7 +9722,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9792,8 +9792,8 @@
       <c r="Y88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z88" s="9" t="n">
-        <v>0</v>
+      <c r="Z88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA88" s="10" t="n">
         <v>1</v>
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9873,7 +9873,7 @@
         <v>0</v>
       </c>
       <c r="S89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T89" s="9" t="n">
         <v>0</v>
@@ -9893,8 +9893,8 @@
       <c r="Y89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z89" s="9" t="n">
-        <v>0</v>
+      <c r="Z89" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA89" s="10" t="n">
         <v>1</v>
@@ -10073,7 +10073,7 @@
         <v>0</v>
       </c>
       <c r="Q91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R91" s="9" t="n">
         <v>0</v>
@@ -10647,7 +10647,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10717,8 +10717,8 @@
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="9" t="n">
-        <v>0</v>
+      <c r="Z97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA97" s="10" t="n">
         <v>1</v>
@@ -11697,7 +11697,7 @@
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11767,8 +11767,8 @@
       <c r="Y107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z107" s="9" t="n">
-        <v>0</v>
+      <c r="Z107" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA107" s="10" t="n">
         <v>1</v>
@@ -11839,16 +11839,16 @@
         </is>
       </c>
       <c r="P108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T108" s="9" t="n">
         <v>0</v>
@@ -12618,7 +12618,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12688,8 +12688,8 @@
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="9" t="n">
-        <v>0</v>
+      <c r="Z116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
@@ -13030,7 +13030,7 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -13100,8 +13100,8 @@
       <c r="Y120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z120" s="9" t="n">
-        <v>0</v>
+      <c r="Z120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA120" s="10" t="n">
         <v>1</v>
@@ -13438,7 +13438,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13508,8 +13508,8 @@
       <c r="Y124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" s="9" t="n">
-        <v>0</v>
+      <c r="Z124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA124" s="10" t="n">
         <v>1</v>
@@ -13543,7 +13543,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13613,8 +13613,8 @@
       <c r="Y125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z125" s="9" t="n">
-        <v>0</v>
+      <c r="Z125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA125" s="10" t="n">
         <v>1</v>
@@ -13848,7 +13848,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13862,13 +13862,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13909,8 +13909,8 @@
       <c r="V128" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W128" s="9" t="n">
-        <v>3</v>
+      <c r="W128" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X128" s="10" t="n">
         <v>7</v>
@@ -14068,13 +14068,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>4</v>
       </c>
       <c r="W130" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X130" s="10" t="n">
         <v>7</v>
@@ -14173,13 +14173,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>69</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>4</v>
       </c>
       <c r="W131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X131" s="10" t="n">
         <v>7</v>
@@ -14987,7 +14987,7 @@
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -15057,8 +15057,8 @@
       <c r="Y139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z139" s="9" t="n">
-        <v>0</v>
+      <c r="Z139" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA139" s="10" t="n">
         <v>1</v>
@@ -15193,7 +15193,7 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -15263,8 +15263,8 @@
       <c r="Y141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="9" t="n">
-        <v>0</v>
+      <c r="Z141" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA141" s="10" t="n">
         <v>1</v>
@@ -15447,7 +15447,7 @@
         <v>2</v>
       </c>
       <c r="Q143" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R143" s="9" t="n">
         <v>0</v>
@@ -15578,8 +15578,8 @@
       <c r="Y144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z144" s="9" t="n">
-        <v>0</v>
+      <c r="Z144" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA144" s="9" t="n">
         <v>0</v>
@@ -15609,7 +15609,7 @@
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -15661,8 +15661,8 @@
       <c r="S145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T145" s="9" t="n">
-        <v>0</v>
+      <c r="T145" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U145" s="9" t="n">
         <v>0</v>
@@ -15815,7 +15815,7 @@
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -15885,8 +15885,8 @@
       <c r="Y147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z147" s="9" t="n">
-        <v>0</v>
+      <c r="Z147" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA147" s="10" t="n">
         <v>1</v>
@@ -15920,7 +15920,7 @@
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>10</v>
@@ -15990,8 +15990,8 @@
       <c r="Y148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z148" s="9" t="n">
-        <v>0</v>
+      <c r="Z148" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA148" s="10" t="n">
         <v>1</v>
@@ -16130,7 +16130,7 @@
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -16144,13 +16144,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
@@ -16188,11 +16188,11 @@
       <c r="U150" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="V150" s="9" t="n">
-        <v>2</v>
+      <c r="V150" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W150" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X150" s="10" t="n">
         <v>6</v>
@@ -16200,8 +16200,8 @@
       <c r="Y150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z150" s="9" t="n">
-        <v>0</v>
+      <c r="Z150" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA150" s="10" t="n">
         <v>1</v>
@@ -16235,7 +16235,7 @@
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -16305,8 +16305,8 @@
       <c r="Y151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z151" s="9" t="n">
-        <v>0</v>
+      <c r="Z151" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA151" s="10" t="n">
         <v>1</v>
@@ -16340,7 +16340,7 @@
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F152" s="6" t="n">
         <v>10</v>
@@ -16410,8 +16410,8 @@
       <c r="Y152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z152" s="9" t="n">
-        <v>0</v>
+      <c r="Z152" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA152" s="10" t="n">
         <v>1</v>
@@ -16546,7 +16546,7 @@
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -16560,13 +16560,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
@@ -16589,8 +16589,8 @@
       <c r="P154" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q154" s="9" t="n">
-        <v>1</v>
+      <c r="Q154" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R154" s="9" t="n">
         <v>0</v>
@@ -16601,14 +16601,14 @@
       <c r="T154" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U154" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V154" s="9" t="n">
-        <v>2</v>
+      <c r="U154" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V154" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W154" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X154" s="10" t="n">
         <v>7</v>
@@ -16721,8 +16721,8 @@
       <c r="Y155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z155" s="9" t="n">
-        <v>0</v>
+      <c r="Z155" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA155" s="9" t="n">
         <v>0</v>
@@ -16861,7 +16861,7 @@
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -16917,7 +16917,7 @@
         <v>1</v>
       </c>
       <c r="U157" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V157" s="9" t="n">
         <v>0</v>
@@ -16931,8 +16931,8 @@
       <c r="Y157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z157" s="9" t="n">
-        <v>0</v>
+      <c r="Z157" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA157" s="10" t="n">
         <v>1</v>
@@ -16966,7 +16966,7 @@
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F158" s="6" t="n">
         <v>10</v>
@@ -16980,13 +16980,13 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>1</v>
       </c>
       <c r="V158" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W158" s="9" t="n">
         <v>0</v>
@@ -17036,8 +17036,8 @@
       <c r="Y158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z158" s="9" t="n">
-        <v>0</v>
+      <c r="Z158" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA158" s="10" t="n">
         <v>1</v>
@@ -17176,7 +17176,7 @@
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -17246,8 +17246,8 @@
       <c r="Y160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z160" s="9" t="n">
-        <v>0</v>
+      <c r="Z160" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA160" s="10" t="n">
         <v>1</v>
@@ -17400,13 +17400,13 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>0</v>
       </c>
       <c r="V162" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W162" s="9" t="n">
         <v>0</v>
@@ -17456,8 +17456,8 @@
       <c r="Y162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z162" s="9" t="n">
-        <v>0</v>
+      <c r="Z162" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA162" s="9" t="n">
         <v>0</v>
@@ -17561,8 +17561,8 @@
       <c r="Y163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z163" s="9" t="n">
-        <v>0</v>
+      <c r="Z163" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA163" s="9" t="n">
         <v>0</v>
@@ -17631,7 +17631,7 @@
         </is>
       </c>
       <c r="P164" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q164" s="9" t="n">
         <v>0</v>
@@ -17689,7 +17689,7 @@
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F165" s="6" t="n">
         <v>10</v>
@@ -17759,8 +17759,8 @@
       <c r="Y165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z165" s="9" t="n">
-        <v>0</v>
+      <c r="Z165" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA165" s="10" t="n">
         <v>1</v>
@@ -17957,8 +17957,8 @@
       <c r="Y167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z167" s="9" t="n">
-        <v>0</v>
+      <c r="Z167" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA167" s="9" t="n">
         <v>0</v>
@@ -18030,7 +18030,7 @@
         <v>0</v>
       </c>
       <c r="Q168" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R168" s="9" t="n">
         <v>0</v>
@@ -18126,7 +18126,7 @@
         </is>
       </c>
       <c r="P169" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q169" s="9" t="n">
         <v>0</v>
@@ -18382,7 +18382,7 @@
         </is>
       </c>
       <c r="E172" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F172" s="6" t="n">
         <v>10</v>
@@ -18452,8 +18452,8 @@
       <c r="Y172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z172" s="9" t="n">
-        <v>0</v>
+      <c r="Z172" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA172" s="10" t="n">
         <v>1</v>
@@ -19215,7 +19215,7 @@
         </is>
       </c>
       <c r="P180" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q180" s="9" t="n">
         <v>0</v>
@@ -19737,7 +19737,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -19770,13 +19770,13 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -19803,7 +19803,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -19968,7 +19968,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -20067,7 +20067,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -20133,7 +20133,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -20232,7 +20232,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -20265,7 +20265,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -20298,7 +20298,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -20331,7 +20331,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -20397,7 +20397,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -20463,7 +20463,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>0.17</v>
+        <v>0.5</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -20529,7 +20529,7 @@
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
         <v>2</v>
@@ -20595,7 +20595,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -20628,7 +20628,7 @@
         <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -20661,13 +20661,13 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -20694,13 +20694,13 @@
         <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -20727,7 +20727,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -20760,7 +20760,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -20826,7 +20826,7 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>

--- a/docs/d/47/inyear.xlsx
+++ b/docs/d/47/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 21 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 21 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 30 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 30 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1270,13 +1270,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" s="9" t="n">
         <v>0</v>
@@ -1371,17 +1371,17 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M7" s="8" t="n">
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" s="10" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1581,13 +1581,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
@@ -1628,8 +1628,8 @@
       <c r="V9" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W9" s="9" t="n">
-        <v>2</v>
+      <c r="W9" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X9" s="10" t="n">
         <v>7</v>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1686,13 +1686,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -1724,8 +1724,8 @@
       <c r="S10" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T10" s="9" t="n">
-        <v>0</v>
+      <c r="T10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U10" s="9" t="n">
         <v>0</v>
@@ -1734,7 +1734,7 @@
         <v>4</v>
       </c>
       <c r="W10" s="10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="X10" s="10" t="n">
         <v>7</v>
@@ -1787,13 +1787,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1888,13 +1888,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2191,13 +2191,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2292,13 +2292,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2330,8 +2330,8 @@
       <c r="S16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T16" s="9" t="n">
-        <v>0</v>
+      <c r="T16" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U16" s="9" t="n">
         <v>0</v>
@@ -2393,17 +2393,17 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M17" s="8" t="n">
@@ -2498,17 +2498,17 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M18" s="8" t="n">
@@ -2801,17 +2801,17 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M21" s="8" t="n">
@@ -2846,7 +2846,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2906,17 +2906,17 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M22" s="8" t="n">
@@ -2936,13 +2936,13 @@
         <v>0</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S22" s="9" t="n">
-        <v>1</v>
+      <c r="S22" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T22" s="10" t="n">
         <v>1</v>
@@ -2951,7 +2951,7 @@
         <v>0</v>
       </c>
       <c r="V22" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W22" s="9" t="n">
         <v>0</v>
@@ -3011,17 +3011,17 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M23" s="8" t="n">
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="P23" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="9" t="n">
         <v>0</v>
@@ -3056,7 +3056,7 @@
         <v>1</v>
       </c>
       <c r="V23" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W23" s="9" t="n">
         <v>0</v>
@@ -3116,13 +3116,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>0</v>
       </c>
       <c r="V24" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W24" s="9" t="n">
         <v>0</v>
@@ -3207,7 +3207,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3221,17 +3221,17 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M25" s="8" t="n">
@@ -3256,8 +3256,8 @@
       <c r="R25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S25" s="9" t="n">
-        <v>1</v>
+      <c r="S25" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T25" s="9" t="n">
         <v>0</v>
@@ -3266,7 +3266,7 @@
         <v>0</v>
       </c>
       <c r="V25" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
@@ -3326,13 +3326,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3431,13 +3431,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4</v>
+        <v>-8</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -3536,17 +3536,17 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M28" s="8" t="n">
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3742,13 +3742,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3843,13 +3843,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
@@ -3948,13 +3948,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -4049,17 +4049,17 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>8</v>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M33" s="8" t="n">
@@ -4093,11 +4093,11 @@
       <c r="U33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" s="9" t="n">
-        <v>0</v>
+      <c r="V33" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W33" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X33" s="9" t="n">
         <v>0</v>
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>0</v>
       </c>
       <c r="V34" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>0</v>
@@ -4249,13 +4249,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4350,17 +4350,17 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M36" s="8" t="n">
@@ -4380,7 +4380,7 @@
         <v>0</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" s="9" t="n">
         <v>0</v>
@@ -4455,17 +4455,17 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M37" s="8" t="n">
@@ -4556,17 +4556,17 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-19</v>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M38" s="8" t="n">
@@ -4661,13 +4661,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>61</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>4</v>
       </c>
       <c r="W39" s="10" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="X39" s="10" t="n">
         <v>6</v>
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4871,13 +4871,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>0</v>
       </c>
       <c r="V41" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
@@ -4972,13 +4972,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>4</v>
       </c>
       <c r="W42" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X42" s="10" t="n">
         <v>5</v>
@@ -5178,13 +5178,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5283,13 +5283,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5485,17 +5485,17 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>47</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-28</v>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M47" s="8" t="n">
@@ -5529,11 +5529,11 @@
       <c r="U47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" s="9" t="n">
-        <v>0</v>
+      <c r="V47" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W47" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X47" s="9" t="n">
         <v>2</v>
@@ -5586,13 +5586,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5687,13 +5687,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -5788,13 +5788,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>4</v>
+        <v>-12</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5893,13 +5893,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>2</v>
       </c>
       <c r="R51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S51" s="9" t="n">
         <v>0</v>
@@ -5937,8 +5937,8 @@
       <c r="U51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V51" s="9" t="n">
-        <v>3</v>
+      <c r="V51" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W51" s="9" t="n">
         <v>0</v>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6099,13 +6099,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
@@ -6143,8 +6143,8 @@
       <c r="U53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V53" s="9" t="n">
-        <v>3</v>
+      <c r="V53" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -6204,13 +6204,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>0</v>
       </c>
       <c r="V54" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W54" s="9" t="n">
         <v>0</v>
@@ -6305,13 +6305,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6410,17 +6410,17 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M56" s="8" t="n">
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="P56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q56" s="9" t="n">
         <v>0</v>
@@ -6446,7 +6446,7 @@
         <v>0</v>
       </c>
       <c r="S56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56" s="10" t="n">
         <v>1</v>
@@ -6515,17 +6515,17 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M57" s="8" t="n">
@@ -6620,17 +6620,17 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M58" s="8" t="n">
@@ -6668,7 +6668,7 @@
         <v>4</v>
       </c>
       <c r="W58" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X58" s="10" t="n">
         <v>5</v>
@@ -6711,7 +6711,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6725,13 +6725,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>7</v>
+        <v>-4</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6772,8 +6772,8 @@
       <c r="V59" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W59" s="9" t="n">
-        <v>3</v>
+      <c r="W59" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X59" s="10" t="n">
         <v>4</v>
@@ -6830,13 +6830,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>0</v>
       </c>
       <c r="V60" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W60" s="9" t="n">
         <v>0</v>
@@ -6935,13 +6935,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -7036,13 +7036,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
@@ -7141,13 +7141,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>4</v>
       </c>
       <c r="W63" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X63" s="9" t="n">
         <v>2</v>
@@ -7242,13 +7242,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>0</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
@@ -7343,13 +7343,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>4</v>
       </c>
       <c r="W65" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X65" s="9" t="n">
         <v>2</v>
@@ -7553,17 +7553,17 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M67" s="8" t="n">
@@ -7644,7 +7644,7 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7658,17 +7658,17 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M68" s="8" t="n">
@@ -7702,8 +7702,8 @@
       <c r="U68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V68" s="9" t="n">
-        <v>2</v>
+      <c r="V68" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7763,17 +7763,17 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M69" s="8" t="n">
@@ -7969,13 +7969,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -8074,13 +8074,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>7</v>
+        <v>-2</v>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
@@ -8179,17 +8179,17 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M73" s="8" t="n">
@@ -8224,7 +8224,7 @@
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -8264,7 +8264,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8278,17 +8278,17 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M74" s="8" t="n">
@@ -8319,11 +8319,11 @@
       <c r="T74" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U74" s="9" t="n">
-        <v>0</v>
+      <c r="U74" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -8383,17 +8383,17 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L75" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M75" s="8" t="n">
@@ -8488,13 +8488,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>4</v>
       </c>
       <c r="W76" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X76" s="10" t="n">
         <v>7</v>
@@ -8589,13 +8589,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>4</v>
       </c>
       <c r="W77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X77" s="10" t="n">
         <v>5</v>
@@ -8694,13 +8694,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
@@ -8799,13 +8799,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>16</v>
+        <v>-1</v>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
@@ -8904,17 +8904,17 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L80" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L80" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M80" s="8" t="n">
@@ -9009,13 +9009,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -9114,17 +9114,17 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L82" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L82" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M82" s="8" t="n">
@@ -9219,17 +9219,17 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M83" s="8" t="n">
@@ -9320,17 +9320,17 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L84" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L84" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M84" s="8" t="n">
@@ -9347,7 +9347,7 @@
         </is>
       </c>
       <c r="P84" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q84" s="9" t="n">
         <v>1</v>
@@ -9425,17 +9425,17 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L85" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L85" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M85" s="8" t="n">
@@ -9530,13 +9530,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9631,13 +9631,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>4</v>
+        <v>-24</v>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>4</v>
       </c>
       <c r="W87" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X87" s="10" t="n">
         <v>5</v>
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9837,13 +9837,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9875,11 +9875,11 @@
       <c r="S89" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T89" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U89" s="9" t="n">
-        <v>0</v>
+      <c r="T89" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U89" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V89" s="9" t="n">
         <v>2</v>
@@ -9938,13 +9938,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         <v>1</v>
       </c>
       <c r="U90" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V90" s="10" t="n">
         <v>4</v>
@@ -10043,13 +10043,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>1</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
@@ -10245,17 +10245,17 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L93" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L93" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M93" s="8" t="n">
@@ -10350,17 +10350,17 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L94" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M94" s="8" t="n">
@@ -10395,7 +10395,7 @@
         <v>0</v>
       </c>
       <c r="V94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W94" s="9" t="n">
         <v>0</v>
@@ -10556,13 +10556,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10661,17 +10661,17 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M97" s="8" t="n">
@@ -10706,7 +10706,7 @@
         <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
@@ -10766,13 +10766,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10796,13 +10796,13 @@
         <v>1</v>
       </c>
       <c r="Q98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R98" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T98" s="10" t="n">
         <v>1</v>
@@ -10871,17 +10871,17 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L99" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M99" s="8" t="n">
@@ -10916,7 +10916,7 @@
         <v>0</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -10962,7 +10962,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10976,13 +10976,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>52</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
@@ -11002,8 +11002,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P100" s="9" t="n">
-        <v>3</v>
+      <c r="P100" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q100" s="9" t="n">
         <v>1</v>
@@ -11018,13 +11018,13 @@
         <v>1</v>
       </c>
       <c r="U100" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V100" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W100" s="10" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="X100" s="10" t="n">
         <v>4</v>
@@ -11081,13 +11081,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         </is>
       </c>
       <c r="P101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q101" s="9" t="n">
         <v>0</v>
@@ -11186,13 +11186,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>8</v>
+        <v>-2</v>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>4</v>
       </c>
       <c r="W102" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X102" s="10" t="n">
         <v>6</v>
@@ -11291,17 +11291,17 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M103" s="8" t="n">
@@ -11336,7 +11336,7 @@
         <v>0</v>
       </c>
       <c r="V103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W103" s="9" t="n">
         <v>0</v>
@@ -11396,13 +11396,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>9</v>
+        <v>-3</v>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         </is>
       </c>
       <c r="P104" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q104" s="9" t="n">
         <v>0</v>
@@ -11444,7 +11444,7 @@
         <v>4</v>
       </c>
       <c r="W104" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X104" s="10" t="n">
         <v>4</v>
@@ -11501,17 +11501,17 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L105" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L105" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M105" s="8" t="n">
@@ -11592,7 +11592,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -11606,13 +11606,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>7</v>
+        <v>-3</v>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
@@ -11653,8 +11653,8 @@
       <c r="V106" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W106" s="9" t="n">
-        <v>3</v>
+      <c r="W106" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X106" s="10" t="n">
         <v>7</v>
@@ -11756,7 +11756,7 @@
         <v>0</v>
       </c>
       <c r="V107" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
@@ -11812,17 +11812,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L108" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L108" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M108" s="8" t="n">
@@ -12000,7 +12000,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -12058,11 +12058,11 @@
       <c r="U110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V110" s="9" t="n">
-        <v>1</v>
+      <c r="V110" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X110" s="10" t="n">
         <v>4</v>
@@ -12093,15 +12093,15 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>1582184</v>
+        <v>1695</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Coconut Grove Toastmasters</t>
+          <t>Coral Gables Toastmasters</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12115,17 +12115,17 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K111" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L111" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L111" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M111" s="8" t="n">
@@ -12142,7 +12142,7 @@
         </is>
       </c>
       <c r="P111" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q111" s="9" t="n">
         <v>0</v>
@@ -12159,14 +12159,14 @@
       <c r="U111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W111" s="9" t="n">
-        <v>0</v>
+      <c r="V111" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W111" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X111" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
@@ -12178,9 +12178,13 @@
         <v>1</v>
       </c>
       <c r="AB111" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC111" s="4" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AC111" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -12194,15 +12198,15 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>1695</v>
+        <v>28679112</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Coral Gables Toastmasters</t>
+          <t>FIU Toastmasters</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12216,13 +12220,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -12243,7 +12247,7 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q112" s="9" t="n">
         <v>0</v>
@@ -12263,11 +12267,11 @@
       <c r="V112" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W112" s="9" t="n">
-        <v>0</v>
+      <c r="W112" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X112" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y112" s="9" t="n">
         <v>0</v>
@@ -12279,13 +12283,9 @@
         <v>1</v>
       </c>
       <c r="AB112" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC112" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC112" s="4" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -12299,11 +12299,11 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>28679112</v>
+        <v>1582184</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>FIU Toastmasters</t>
+          <t>Pinecrest Hybrid Toastmasters</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -12366,13 +12366,13 @@
         <v>0</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X113" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y113" s="9" t="n">
         <v>0</v>
@@ -12384,7 +12384,7 @@
         <v>1</v>
       </c>
       <c r="AB113" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AC113" s="4" t="inlineStr"/>
     </row>
@@ -12408,7 +12408,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12422,13 +12422,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>0</v>
       </c>
       <c r="S114" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T114" s="10" t="n">
         <v>1</v>
@@ -12466,11 +12466,11 @@
       <c r="U114" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V114" s="9" t="n">
-        <v>2</v>
+      <c r="V114" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X114" s="10" t="n">
         <v>5</v>
@@ -12513,7 +12513,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12527,13 +12527,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
@@ -12574,8 +12574,8 @@
       <c r="V115" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W115" s="9" t="n">
-        <v>3</v>
+      <c r="W115" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X115" s="10" t="n">
         <v>7</v>
@@ -12632,13 +12632,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -12733,13 +12733,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12834,17 +12834,17 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L118" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L118" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M118" s="8" t="n">
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12939,17 +12939,17 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L119" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M119" s="8" t="n">
@@ -12983,11 +12983,11 @@
       <c r="U119" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V119" s="9" t="n">
-        <v>0</v>
+      <c r="V119" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X119" s="10" t="n">
         <v>7</v>
@@ -13044,13 +13044,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>-1</v>
+        <v>-10</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>0</v>
       </c>
       <c r="V120" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
@@ -13145,17 +13145,17 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L121" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M121" s="8" t="n">
@@ -13250,13 +13250,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -13351,13 +13351,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -13452,17 +13452,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-16</v>
+      </c>
+      <c r="L124" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M124" s="8" t="n">
@@ -13557,17 +13557,17 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L125" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M125" s="8" t="n">
@@ -13797,7 +13797,7 @@
         <v>0</v>
       </c>
       <c r="S127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T127" s="9" t="n">
         <v>0</v>
@@ -13862,13 +13862,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>4</v>
       </c>
       <c r="W128" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X128" s="10" t="n">
         <v>7</v>
@@ -13967,13 +13967,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
@@ -14054,7 +14054,7 @@
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -14068,13 +14068,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>5</v>
+        <v>-11</v>
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
@@ -14100,8 +14100,8 @@
       <c r="Q130" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R130" s="9" t="n">
-        <v>1</v>
+      <c r="R130" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S130" s="9" t="n">
         <v>1</v>
@@ -14116,7 +14116,7 @@
         <v>4</v>
       </c>
       <c r="W130" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X130" s="10" t="n">
         <v>7</v>
@@ -14173,13 +14173,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>69</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>5</v>
+        <v>-19</v>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>2</v>
       </c>
       <c r="S131" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T131" s="10" t="n">
         <v>1</v>
@@ -14278,17 +14278,17 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L132" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L132" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M132" s="8" t="n">
@@ -14383,17 +14383,17 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L133" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M133" s="8" t="n">
@@ -14488,17 +14488,17 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L134" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L134" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M134" s="8" t="n">
@@ -14518,7 +14518,7 @@
         <v>0</v>
       </c>
       <c r="Q134" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R134" s="9" t="n">
         <v>0</v>
@@ -14593,13 +14593,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
@@ -14694,17 +14694,17 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L136" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-19</v>
+      </c>
+      <c r="L136" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M136" s="8" t="n">
@@ -15001,17 +15001,17 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L139" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L139" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M139" s="8" t="n">
@@ -15207,17 +15207,17 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L141" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L141" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M141" s="8" t="n">
@@ -15312,17 +15312,17 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L142" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L142" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M142" s="8" t="n">
@@ -15417,17 +15417,17 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L143" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L143" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M143" s="8" t="n">
@@ -15508,7 +15508,7 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -15522,13 +15522,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -15560,8 +15560,8 @@
       <c r="S144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T144" s="9" t="n">
-        <v>0</v>
+      <c r="T144" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U144" s="9" t="n">
         <v>0</v>
@@ -15623,13 +15623,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
@@ -15668,7 +15668,7 @@
         <v>0</v>
       </c>
       <c r="V145" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W145" s="9" t="n">
         <v>0</v>
@@ -15724,17 +15724,17 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L146" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L146" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M146" s="8" t="n">
@@ -15769,7 +15769,7 @@
         <v>1</v>
       </c>
       <c r="V146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W146" s="9" t="n">
         <v>0</v>
@@ -15829,17 +15829,17 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L147" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L147" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M147" s="8" t="n">
@@ -15934,17 +15934,17 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L148" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L148" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M148" s="8" t="n">
@@ -15979,7 +15979,7 @@
         <v>1</v>
       </c>
       <c r="V148" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W148" s="9" t="n">
         <v>0</v>
@@ -16039,17 +16039,17 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L149" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-17</v>
+      </c>
+      <c r="L149" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M149" s="8" t="n">
@@ -16144,17 +16144,17 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L150" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L150" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M150" s="8" t="n">
@@ -16249,17 +16249,17 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L151" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L151" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M151" s="8" t="n">
@@ -16354,17 +16354,17 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L152" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L152" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M152" s="8" t="n">
@@ -16459,13 +16459,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
@@ -16560,17 +16560,17 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L154" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L154" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M154" s="8" t="n">
@@ -16665,17 +16665,17 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L155" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L155" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M155" s="8" t="n">
@@ -16770,13 +16770,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L156" s="7" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>1</v>
       </c>
       <c r="V156" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W156" s="9" t="n">
         <v>0</v>
@@ -16875,17 +16875,17 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L157" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L157" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M157" s="8" t="n">
@@ -16980,17 +16980,17 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L158" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L158" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M158" s="8" t="n">
@@ -17071,7 +17071,7 @@
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>10</v>
@@ -17085,17 +17085,17 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L159" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L159" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M159" s="8" t="n">
@@ -17129,11 +17129,11 @@
       <c r="U159" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V159" s="9" t="n">
-        <v>3</v>
+      <c r="V159" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W159" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X159" s="10" t="n">
         <v>6</v>
@@ -17190,17 +17190,17 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L160" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L160" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M160" s="8" t="n">
@@ -17295,13 +17295,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>54</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="L161" s="4" t="inlineStr">
         <is>
@@ -17400,17 +17400,17 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L162" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L162" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M162" s="8" t="n">
@@ -17445,7 +17445,7 @@
         <v>0</v>
       </c>
       <c r="V162" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W162" s="9" t="n">
         <v>0</v>
@@ -17505,17 +17505,17 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L163" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L163" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M163" s="8" t="n">
@@ -17604,13 +17604,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
@@ -17703,13 +17703,13 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L165" s="7" t="inlineStr">
         <is>
@@ -17887,7 +17887,7 @@
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>10</v>
@@ -17901,17 +17901,17 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L167" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>8</v>
+      </c>
+      <c r="L167" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M167" s="8" t="n">
@@ -17945,11 +17945,11 @@
       <c r="U167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V167" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W167" s="9" t="n">
-        <v>0</v>
+      <c r="V167" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W167" s="10" t="n">
+        <v>13</v>
       </c>
       <c r="X167" s="9" t="n">
         <v>0</v>
@@ -18048,7 +18048,7 @@
         <v>4</v>
       </c>
       <c r="W168" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X168" s="10" t="n">
         <v>4</v>
@@ -18099,17 +18099,17 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L169" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L169" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M169" s="8" t="n">
@@ -18147,7 +18147,7 @@
         <v>4</v>
       </c>
       <c r="W169" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X169" s="9" t="n">
         <v>0</v>
@@ -18198,13 +18198,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L170" s="7" t="inlineStr">
         <is>
@@ -18246,7 +18246,7 @@
         <v>4</v>
       </c>
       <c r="W170" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X170" s="9" t="n">
         <v>2</v>
@@ -18297,13 +18297,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L171" s="4" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>0</v>
       </c>
       <c r="V171" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W171" s="9" t="n">
         <v>0</v>
@@ -18396,13 +18396,13 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
@@ -18594,13 +18594,13 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L174" s="7" t="inlineStr">
         <is>
@@ -18792,13 +18792,13 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J176" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>0</v>
       </c>
       <c r="V176" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W176" s="9" t="n">
         <v>0</v>
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         </is>
       </c>
       <c r="E178" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F178" s="6" t="n">
         <v>10</v>
@@ -18990,13 +18990,13 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J178" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
@@ -19034,11 +19034,11 @@
       <c r="U178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V178" s="9" t="n">
-        <v>0</v>
+      <c r="V178" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W178" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X178" s="10" t="n">
         <v>6</v>
@@ -19089,13 +19089,13 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J179" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>8</v>
+        <v>-4</v>
       </c>
       <c r="L179" s="4" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>4</v>
       </c>
       <c r="W179" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X179" s="10" t="n">
         <v>7</v>
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="E180" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F180" s="6" t="n">
         <v>10</v>
@@ -19188,17 +19188,17 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J180" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L180" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L180" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M180" s="8" t="n">
@@ -19232,8 +19232,8 @@
       <c r="U180" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V180" s="9" t="n">
-        <v>3</v>
+      <c r="V180" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W180" s="9" t="n">
         <v>0</v>
@@ -19287,13 +19287,13 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J181" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K181" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L181" s="7" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>0</v>
       </c>
       <c r="V181" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W181" s="9" t="n">
         <v>0</v>
@@ -19386,17 +19386,17 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J182" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L182" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L182" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M182" s="8" t="n">
@@ -19485,13 +19485,13 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="J183" s="4" t="n">
         <v>47</v>
       </c>
       <c r="K183" s="4" t="n">
-        <v>6</v>
+        <v>-6</v>
       </c>
       <c r="L183" s="4" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>4</v>
       </c>
       <c r="W183" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X183" s="10" t="n">
         <v>5</v>
@@ -19570,7 +19570,7 @@
         </is>
       </c>
       <c r="E184" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F184" s="6" t="n">
         <v>10</v>
@@ -19584,13 +19584,13 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="J184" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>7</v>
+        <v>-8</v>
       </c>
       <c r="L184" s="4" t="inlineStr">
         <is>
@@ -19631,8 +19631,8 @@
       <c r="V184" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W184" s="9" t="n">
-        <v>3</v>
+      <c r="W184" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X184" s="9" t="n">
         <v>1</v>
@@ -19752,7 +19752,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -19770,7 +19770,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -19803,7 +19803,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -19818,7 +19818,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -19836,7 +19836,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -19851,7 +19851,7 @@
         <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -19869,7 +19869,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -19884,7 +19884,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -19902,7 +19902,7 @@
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -19950,7 +19950,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -20001,7 +20001,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -20016,7 +20016,7 @@
         <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -20034,13 +20034,13 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -20082,7 +20082,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -20100,7 +20100,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -20148,7 +20148,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -20166,7 +20166,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -20181,7 +20181,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -20199,7 +20199,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -20214,7 +20214,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -20247,7 +20247,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -20280,7 +20280,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -20298,7 +20298,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -20313,7 +20313,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -20346,7 +20346,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -20364,7 +20364,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -20379,7 +20379,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -20397,7 +20397,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -20412,7 +20412,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -20430,22 +20430,22 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>4</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -20463,7 +20463,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -20478,7 +20478,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -20511,7 +20511,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -20529,7 +20529,7 @@
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="E26" t="n">
         <v>2</v>
@@ -20544,7 +20544,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -20577,7 +20577,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -20610,7 +20610,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -20628,7 +20628,7 @@
         <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -20643,7 +20643,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -20676,7 +20676,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -20709,7 +20709,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -20727,7 +20727,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -20742,7 +20742,7 @@
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -20760,7 +20760,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -20808,7 +20808,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -20859,7 +20859,7 @@
         <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
@@ -20874,7 +20874,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -20892,7 +20892,7 @@
         <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -20907,7 +20907,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/47/inyear.xlsx
+++ b/docs/d/47/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/47/inyear.xlsx
+++ b/docs/d/47/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/47/inyear.xlsx
+++ b/docs/d/47/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/47/inyear.xlsx
+++ b/docs/d/47/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/47/inyear.xlsx
+++ b/docs/d/47/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$184</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$185</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 21 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 21 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 30 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 30 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC184"/>
+  <dimension ref="A1:AC185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1581,13 +1581,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>4</v>
       </c>
       <c r="W9" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X9" s="10" t="n">
         <v>7</v>
@@ -1686,13 +1686,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>2</v>
       </c>
       <c r="R10" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S10" s="10" t="n">
         <v>2</v>
@@ -1734,7 +1734,7 @@
         <v>4</v>
       </c>
       <c r="W10" s="10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X10" s="10" t="n">
         <v>7</v>
@@ -1787,13 +1787,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>4</v>
       </c>
       <c r="W11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" s="10" t="n">
         <v>7</v>
@@ -2393,13 +2393,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>2</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="9" t="n">
         <v>0</v>
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2839,11 +2839,11 @@
       <c r="S21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" s="9" t="n">
-        <v>0</v>
+      <c r="T21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V21" s="9" t="n">
         <v>1</v>
@@ -2892,7 +2892,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2906,13 +2906,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-13</v>
+        <v>-11</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -2950,8 +2950,8 @@
       <c r="U22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V22" s="9" t="n">
-        <v>3</v>
+      <c r="V22" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W22" s="9" t="n">
         <v>0</v>
@@ -3011,13 +3011,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>1</v>
       </c>
       <c r="V23" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W23" s="9" t="n">
         <v>0</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="P24" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q24" s="9" t="n">
         <v>0</v>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -4455,13 +4455,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4661,13 +4661,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>61</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4998,8 +4998,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P42" s="9" t="n">
-        <v>3</v>
+      <c r="P42" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q42" s="9" t="n">
         <v>0</v>
@@ -5008,7 +5008,7 @@
         <v>0</v>
       </c>
       <c r="S42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T42" s="10" t="n">
         <v>1</v>
@@ -5283,13 +5283,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5586,13 +5586,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -6099,13 +6099,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
@@ -6515,17 +6515,17 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L57" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M57" s="8" t="n">
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="V57" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>0</v>
@@ -6725,13 +6725,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6859,8 +6859,8 @@
       <c r="P60" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="Q60" s="9" t="n">
-        <v>1</v>
+      <c r="Q60" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R60" s="9" t="n">
         <v>0</v>
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -7141,13 +7141,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         </is>
       </c>
       <c r="P63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q63" s="9" t="n">
         <v>0</v>
@@ -7188,8 +7188,8 @@
       <c r="V63" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W63" s="9" t="n">
-        <v>3</v>
+      <c r="W63" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X63" s="9" t="n">
         <v>2</v>
@@ -8005,7 +8005,7 @@
         <v>0</v>
       </c>
       <c r="S71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T71" s="9" t="n">
         <v>0</v>
@@ -8215,7 +8215,7 @@
         <v>1</v>
       </c>
       <c r="S73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T73" s="9" t="n">
         <v>0</v>
@@ -8589,13 +8589,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9463,8 +9463,8 @@
       <c r="S85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T85" s="9" t="n">
-        <v>0</v>
+      <c r="T85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U85" s="9" t="n">
         <v>0</v>
@@ -10976,13 +10976,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>52</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>-16</v>
+        <v>-11</v>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>0</v>
       </c>
       <c r="S100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T100" s="10" t="n">
         <v>1</v>
@@ -11291,13 +11291,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11396,13 +11396,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
@@ -11431,8 +11431,8 @@
       <c r="R104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S104" s="9" t="n">
-        <v>1</v>
+      <c r="S104" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T104" s="10" t="n">
         <v>1</v>
@@ -11444,7 +11444,7 @@
         <v>4</v>
       </c>
       <c r="W104" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X104" s="10" t="n">
         <v>4</v>
@@ -11475,43 +11475,43 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>4555744</v>
+        <v>28681080</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Bold Communicators Club</t>
+          <t>OYC Miami</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I105" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="J105" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="K105" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F105" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G105" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H105" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I105" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="J105" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K105" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L105" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L105" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M105" s="8" t="n">
@@ -11528,31 +11528,31 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q105" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S105" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T105" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T105" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X105" s="10" t="n">
-        <v>7</v>
+      <c r="X105" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y105" s="9" t="n">
         <v>0</v>
@@ -11561,16 +11561,10 @@
         <v>1</v>
       </c>
       <c r="AA105" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB105" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC105" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AB105" s="4" t="n"/>
+      <c r="AC105" s="4" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -11584,15 +11578,15 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>861</v>
+        <v>4555744</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Doral Toastmasters</t>
+          <t>Bold Communicators Club</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -11606,17 +11600,17 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="K106" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="L106" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L106" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M106" s="8" t="n">
@@ -11635,26 +11629,26 @@
       <c r="P106" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q106" s="10" t="n">
-        <v>2</v>
+      <c r="Q106" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="R106" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S106" s="10" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="S106" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="T106" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U106" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V106" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W106" s="10" t="n">
-        <v>4</v>
+      <c r="U106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W106" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X106" s="10" t="n">
         <v>7</v>
@@ -11669,11 +11663,11 @@
         <v>1</v>
       </c>
       <c r="AB106" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC106" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -11689,15 +11683,15 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>28678307</v>
+        <v>861</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>MDCR Fantastic Speakers</t>
+          <t>Doral Toastmasters</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11711,17 +11705,17 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L107" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-3</v>
+      </c>
+      <c r="L107" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M107" s="8" t="n">
@@ -11738,31 +11732,31 @@
         </is>
       </c>
       <c r="P107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q107" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V107" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="S107" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T107" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U107" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V107" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W107" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X107" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y107" s="9" t="n">
         <v>0</v>
@@ -11774,9 +11768,13 @@
         <v>1</v>
       </c>
       <c r="AB107" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC107" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC107" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -11790,11 +11788,11 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>2283</v>
+        <v>28678307</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Miracle Mile Toastmasters Club</t>
+          <t>MDCR Fantastic Speakers</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
@@ -11812,13 +11810,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J108" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11839,16 +11837,16 @@
         </is>
       </c>
       <c r="P108" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q108" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S108" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T108" s="9" t="n">
         <v>0</v>
@@ -11875,7 +11873,7 @@
         <v>1</v>
       </c>
       <c r="AB108" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AC108" s="4" t="inlineStr"/>
     </row>
@@ -11891,11 +11889,11 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>28678131</v>
+        <v>2283</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Telemundo Center Toastmasters</t>
+          <t>Miracle Mile Toastmasters Club</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
@@ -11913,13 +11911,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11940,16 +11938,16 @@
         </is>
       </c>
       <c r="P109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T109" s="9" t="n">
         <v>0</v>
@@ -11958,7 +11956,7 @@
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -11976,7 +11974,7 @@
         <v>1</v>
       </c>
       <c r="AB109" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AC109" s="4" t="inlineStr"/>
     </row>
@@ -11992,15 +11990,15 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>7082</v>
+        <v>28678131</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Voice Of Champions Club</t>
+          <t>Telemundo Center Toastmasters</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -12014,10 +12012,10 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K110" s="4" t="n">
         <v>0</v>
@@ -12041,10 +12039,10 @@
         </is>
       </c>
       <c r="P110" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R110" s="9" t="n">
         <v>0</v>
@@ -12052,17 +12050,17 @@
       <c r="S110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T110" s="10" t="n">
-        <v>1</v>
+      <c r="T110" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V110" s="10" t="n">
-        <v>4</v>
+      <c r="V110" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W110" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X110" s="10" t="n">
         <v>4</v>
@@ -12077,7 +12075,7 @@
         <v>1</v>
       </c>
       <c r="AB110" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC110" s="4" t="inlineStr"/>
     </row>
@@ -12089,19 +12087,19 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>1695</v>
+        <v>7082</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Coral Gables Toastmasters</t>
+          <t>Voice Of Champions Club</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12115,17 +12113,17 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L111" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M111" s="8" t="n">
@@ -12142,7 +12140,7 @@
         </is>
       </c>
       <c r="P111" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q111" s="9" t="n">
         <v>0</v>
@@ -12153,38 +12151,34 @@
       <c r="S111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U111" s="9" t="n">
-        <v>0</v>
+      <c r="T111" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V111" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W111" s="10" t="n">
+      <c r="W111" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="X111" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="X111" s="10" t="n">
+      <c r="Y111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z111" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA111" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB111" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="Y111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z111" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA111" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB111" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC111" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+      <c r="AC111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -12198,15 +12192,15 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>28679112</v>
+        <v>1695</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>FIU Toastmasters</t>
+          <t>Coral Gables Toastmasters</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12220,13 +12214,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -12246,8 +12240,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P112" s="9" t="n">
-        <v>0</v>
+      <c r="P112" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q112" s="9" t="n">
         <v>0</v>
@@ -12256,7 +12250,7 @@
         <v>0</v>
       </c>
       <c r="S112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T112" s="9" t="n">
         <v>0</v>
@@ -12268,10 +12262,10 @@
         <v>4</v>
       </c>
       <c r="W112" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="X112" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y112" s="9" t="n">
         <v>0</v>
@@ -12283,9 +12277,13 @@
         <v>1</v>
       </c>
       <c r="AB112" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC112" s="4" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AC112" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -12299,15 +12297,15 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>1582184</v>
+        <v>28679112</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Pinecrest Hybrid Toastmasters</t>
+          <t>FIU Toastmasters</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -12321,17 +12319,17 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="J113" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="J113" s="4" t="n">
-        <v>12</v>
-      </c>
       <c r="K113" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L113" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>9</v>
+      </c>
+      <c r="L113" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M113" s="8" t="n">
@@ -12365,14 +12363,14 @@
       <c r="U113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V113" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W113" s="9" t="n">
-        <v>0</v>
+      <c r="V113" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W113" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="X113" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y113" s="9" t="n">
         <v>0</v>
@@ -12384,7 +12382,7 @@
         <v>1</v>
       </c>
       <c r="AB113" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AC113" s="4" t="inlineStr"/>
     </row>
@@ -12400,15 +12398,15 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>2463</v>
+        <v>1582184</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>South Dade Toastmasters Club</t>
+          <t>Pinecrest Hybrid Toastmasters</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12422,17 +12420,17 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L114" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L114" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M114" s="8" t="n">
@@ -12449,7 +12447,7 @@
         </is>
       </c>
       <c r="P114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q114" s="9" t="n">
         <v>0</v>
@@ -12457,23 +12455,23 @@
       <c r="R114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S114" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T114" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U114" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V114" s="10" t="n">
-        <v>4</v>
+      <c r="S114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V114" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W114" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X114" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y114" s="9" t="n">
         <v>0</v>
@@ -12485,13 +12483,9 @@
         <v>1</v>
       </c>
       <c r="AB114" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC114" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="AC114" s="4" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -12505,15 +12499,15 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>8370</v>
+        <v>2463</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>West Kendall Toastmasters Club 8370</t>
+          <t>South Dade Toastmasters Club</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12527,10 +12521,10 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="K115" s="4" t="n">
         <v>1</v>
@@ -12553,32 +12547,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P115" s="10" t="n">
+      <c r="P115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q115" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R115" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S115" s="10" t="n">
+      <c r="T115" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U115" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="T115" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U115" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="V115" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W115" s="10" t="n">
-        <v>4</v>
+      <c r="W115" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="X115" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y115" s="9" t="n">
         <v>0</v>
@@ -12606,19 +12600,19 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>1412303</v>
+        <v>8370</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Cutler Bay Toastmasters</t>
+          <t>West Kendall Toastmasters Club 8370</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12632,17 +12626,17 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L116" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M116" s="8" t="n">
@@ -12658,32 +12652,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P116" s="9" t="n">
-        <v>0</v>
+      <c r="P116" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T116" s="9" t="n">
-        <v>0</v>
+      <c r="S116" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V116" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W116" s="9" t="n">
-        <v>0</v>
+      <c r="V116" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W116" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X116" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
@@ -12695,9 +12689,13 @@
         <v>1</v>
       </c>
       <c r="AB116" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC116" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC116" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -12711,11 +12709,11 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>704393</v>
+        <v>1412303</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Florida  Keys Toastmasters</t>
+          <t>Cutler Bay Toastmasters</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
@@ -12736,10 +12734,10 @@
         <v>9</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12778,13 +12776,13 @@
         <v>0</v>
       </c>
       <c r="V117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X117" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y117" s="9" t="n">
         <v>0</v>
@@ -12796,7 +12794,7 @@
         <v>1</v>
       </c>
       <c r="AB117" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC117" s="4" t="inlineStr"/>
     </row>
@@ -12812,15 +12810,15 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>6298</v>
+        <v>704393</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Key West Toastmasters</t>
+          <t>Florida  Keys Toastmasters</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12834,13 +12832,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-10</v>
+        <v>-1</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -12870,16 +12868,16 @@
         <v>0</v>
       </c>
       <c r="S118" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T118" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T118" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U118" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V118" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W118" s="9" t="n">
         <v>0</v>
@@ -12897,13 +12895,9 @@
         <v>1</v>
       </c>
       <c r="AB118" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC118" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AC118" s="4" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -12917,15 +12911,15 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>2798</v>
+        <v>6298</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Miami Advanced Toastmasters Club</t>
+          <t>Key West Toastmasters</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12939,13 +12933,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -12969,28 +12963,28 @@
         <v>0</v>
       </c>
       <c r="Q119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T119" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U119" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V119" s="10" t="n">
-        <v>4</v>
+      <c r="U119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V119" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W119" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X119" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y119" s="9" t="n">
         <v>0</v>
@@ -13002,11 +12996,11 @@
         <v>1</v>
       </c>
       <c r="AB119" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC119" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -13022,15 +13016,15 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>28679707</v>
+        <v>2798</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>OneADP Miami</t>
+          <t>Miami Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -13044,13 +13038,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -13082,20 +13076,20 @@
       <c r="S120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T120" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U120" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V120" s="9" t="n">
-        <v>3</v>
+      <c r="T120" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U120" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V120" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X120" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
@@ -13107,27 +13101,31 @@
         <v>1</v>
       </c>
       <c r="AB120" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC120" s="4" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AC120" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>1095</v>
+        <v>28679707</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Action For Achievement Club 1095</t>
+          <t>OneADP Miami</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
@@ -13148,10 +13146,10 @@
         <v>10</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -13172,7 +13170,7 @@
         </is>
       </c>
       <c r="P121" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q121" s="9" t="n">
         <v>0</v>
@@ -13190,13 +13188,13 @@
         <v>0</v>
       </c>
       <c r="V121" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X121" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y121" s="9" t="n">
         <v>0</v>
@@ -13208,13 +13206,9 @@
         <v>1</v>
       </c>
       <c r="AB121" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC121" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC121" s="4" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
@@ -13228,15 +13222,15 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>6796</v>
+        <v>1095</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>BAMSI Club Altitude</t>
+          <t>Action For Achievement Club 1095</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13250,13 +13244,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>-5</v>
+        <v>-12</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -13277,7 +13271,7 @@
         </is>
       </c>
       <c r="P122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q122" s="9" t="n">
         <v>0</v>
@@ -13295,27 +13289,31 @@
         <v>0</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X122" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z122" s="9" t="n">
-        <v>0</v>
+      <c r="Z122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA122" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB122" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC122" s="4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="AC122" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -13329,11 +13327,11 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>971904</v>
+        <v>6796</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Chickcharney Toastmasters Club</t>
+          <t>BAMSI Club Altitude</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
@@ -13351,13 +13349,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -13387,7 +13385,7 @@
         <v>0</v>
       </c>
       <c r="S123" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T123" s="9" t="n">
         <v>0</v>
@@ -13396,7 +13394,7 @@
         <v>0</v>
       </c>
       <c r="V123" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
@@ -13414,7 +13412,7 @@
         <v>1</v>
       </c>
       <c r="AB123" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC123" s="4" t="inlineStr"/>
     </row>
@@ -13430,15 +13428,15 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>7875684</v>
+        <v>971904</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Leading Voices Toastmasters Club</t>
+          <t>Chickcharney Toastmasters Club</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13452,13 +13450,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-16</v>
+        <v>-2</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -13479,10 +13477,10 @@
         </is>
       </c>
       <c r="P124" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q124" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R124" s="9" t="n">
         <v>0</v>
@@ -13503,25 +13501,21 @@
         <v>0</v>
       </c>
       <c r="X124" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" s="10" t="n">
-        <v>1</v>
+      <c r="Z124" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA124" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB124" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC124" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AC124" s="4" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -13535,11 +13529,11 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>1510789</v>
+        <v>7875684</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Luminaries Toastmasters Club #1510789</t>
+          <t>Leading Voices Toastmasters Club</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
@@ -13557,13 +13551,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>-14</v>
+        <v>-16</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -13584,16 +13578,16 @@
         </is>
       </c>
       <c r="P125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T125" s="9" t="n">
         <v>0</v>
@@ -13608,7 +13602,7 @@
         <v>0</v>
       </c>
       <c r="X125" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
@@ -13620,11 +13614,11 @@
         <v>1</v>
       </c>
       <c r="AB125" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC125" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -13640,15 +13634,15 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>28680767</v>
+        <v>1510789</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>The Leadership Lounge at Baha Mar</t>
+          <t>Luminaries Toastmasters Club #1510789</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -13662,17 +13656,17 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="J126" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="J126" s="4" t="n">
-        <v>20</v>
-      </c>
       <c r="K126" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L126" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L126" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M126" s="8" t="n">
@@ -13713,19 +13707,25 @@
         <v>0</v>
       </c>
       <c r="X126" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z126" s="9" t="n">
-        <v>0</v>
+      <c r="Z126" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA126" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB126" s="4" t="n"/>
-      <c r="AC126" s="4" t="inlineStr"/>
+      <c r="AB126" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC126" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -13735,15 +13735,15 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>28680429</v>
+        <v>28680767</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>BRON Blazers</t>
+          <t>The Leadership Lounge at Baha Mar</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
@@ -13764,10 +13764,10 @@
         <v>22</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
@@ -13797,7 +13797,7 @@
         <v>0</v>
       </c>
       <c r="S127" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T127" s="9" t="n">
         <v>0</v>
@@ -13806,13 +13806,13 @@
         <v>0</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X127" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y127" s="9" t="n">
         <v>0</v>
@@ -13823,9 +13823,7 @@
       <c r="AA127" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB127" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB127" s="4" t="n"/>
       <c r="AC127" s="4" t="inlineStr"/>
     </row>
     <row r="128">
@@ -13840,15 +13838,15 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>2591529</v>
+        <v>28680429</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Cable Revolutionaries Toastmasters Club 2591529</t>
+          <t>BRON Blazers</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13862,13 +13860,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13889,49 +13887,45 @@
         </is>
       </c>
       <c r="P128" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q128" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S128" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T128" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U128" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V128" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W128" s="10" t="n">
+      <c r="S128" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X128" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="X128" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z128" s="10" t="n">
-        <v>1</v>
+      <c r="Z128" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA128" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB128" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC128" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC128" s="4" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -13945,15 +13939,15 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>28680489</v>
+        <v>2591529</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Elite Executives</t>
+          <t>Cable Revolutionaries Toastmasters Club 2591529</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13967,13 +13961,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
@@ -13993,29 +13987,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q129" s="9" t="n">
-        <v>0</v>
+      <c r="P129" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q129" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V129" s="9" t="n">
+      <c r="S129" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="W129" s="9" t="n">
-        <v>0</v>
+      <c r="T129" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U129" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V129" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W129" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X129" s="10" t="n">
         <v>7</v>
@@ -14030,9 +14024,13 @@
         <v>1</v>
       </c>
       <c r="AB129" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC129" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC129" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -14046,15 +14044,15 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>4719842</v>
+        <v>28680489</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>FG Knights</t>
+          <t>Elite Executives</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -14068,13 +14066,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>-11</v>
+        <v>1</v>
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
@@ -14095,28 +14093,28 @@
         </is>
       </c>
       <c r="P130" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q130" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V130" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="R130" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S130" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V130" s="10" t="n">
-        <v>4</v>
-      </c>
       <c r="W130" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X130" s="10" t="n">
         <v>7</v>
@@ -14131,13 +14129,9 @@
         <v>1</v>
       </c>
       <c r="AB130" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC130" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC130" s="4" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -14151,15 +14145,15 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>7178</v>
+        <v>4719842</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Healing Communicators Club</t>
+          <t>FG Knights</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -14173,13 +14167,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>-19</v>
+        <v>-10</v>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
@@ -14200,7 +14194,7 @@
         </is>
       </c>
       <c r="P131" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q131" s="10" t="n">
         <v>2</v>
@@ -14208,20 +14202,20 @@
       <c r="R131" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="S131" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T131" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U131" s="10" t="n">
-        <v>2</v>
+      <c r="S131" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U131" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V131" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W131" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X131" s="10" t="n">
         <v>7</v>
@@ -14256,15 +14250,15 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>7773041</v>
+        <v>7178</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Pinewood Trendsetters</t>
+          <t>Healing Communicators Club</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14278,17 +14272,17 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>-15</v>
-      </c>
-      <c r="L132" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-19</v>
+      </c>
+      <c r="L132" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M132" s="8" t="n">
@@ -14305,28 +14299,28 @@
         </is>
       </c>
       <c r="P132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V132" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Q132" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R132" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S132" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T132" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U132" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V132" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X132" s="10" t="n">
         <v>7</v>
@@ -14357,15 +14351,15 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>1358961</v>
+        <v>7773041</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>B.U.T. Nation Builders</t>
+          <t>Pinewood Trendsetters</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
@@ -14383,13 +14377,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
@@ -14410,10 +14404,10 @@
         </is>
       </c>
       <c r="P133" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q133" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R133" s="9" t="n">
         <v>0</v>
@@ -14428,7 +14422,7 @@
         <v>0</v>
       </c>
       <c r="V133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W133" s="9" t="n">
         <v>0</v>
@@ -14466,15 +14460,15 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>7717904</v>
+        <v>1358961</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>East Central Archdeaconry</t>
+          <t>B.U.T. Nation Builders</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -14488,13 +14482,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -14515,7 +14509,7 @@
         </is>
       </c>
       <c r="P134" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q134" s="9" t="n">
         <v>1</v>
@@ -14532,11 +14526,11 @@
       <c r="U134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V134" s="10" t="n">
-        <v>4</v>
+      <c r="V134" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W134" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X134" s="10" t="n">
         <v>7</v>
@@ -14571,15 +14565,15 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>8123</v>
+        <v>7717904</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>First Exuma Branch Club 8123</t>
+          <t>East Central Archdeaconry</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -14593,17 +14587,17 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L135" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-7</v>
+      </c>
+      <c r="L135" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M135" s="8" t="n">
@@ -14623,7 +14617,7 @@
         <v>0</v>
       </c>
       <c r="Q135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R135" s="9" t="n">
         <v>0</v>
@@ -14637,28 +14631,32 @@
       <c r="U135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V135" s="9" t="n">
-        <v>2</v>
+      <c r="V135" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X135" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z135" s="9" t="n">
-        <v>0</v>
+      <c r="Z135" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA135" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB135" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC135" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC135" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -14672,15 +14670,15 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>7180193</v>
+        <v>8123</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Legalites</t>
+          <t>First Exuma Branch Club 8123</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -14694,13 +14692,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>-19</v>
+        <v>-5</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -14732,20 +14730,20 @@
       <c r="S136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T136" s="10" t="n">
-        <v>1</v>
+      <c r="T136" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U136" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V136" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X136" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y136" s="9" t="n">
         <v>0</v>
@@ -14757,13 +14755,9 @@
         <v>1</v>
       </c>
       <c r="AB136" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC136" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC136" s="4" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -14777,15 +14771,15 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>28680490</v>
+        <v>7180193</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Modern Pillars of Excellence</t>
+          <t>Legalites</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -14799,17 +14793,17 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L137" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-19</v>
+      </c>
+      <c r="L137" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M137" s="8" t="n">
@@ -14837,20 +14831,20 @@
       <c r="S137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T137" s="9" t="n">
-        <v>0</v>
+      <c r="T137" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U137" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V137" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W137" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X137" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y137" s="9" t="n">
         <v>0</v>
@@ -14862,9 +14856,13 @@
         <v>1</v>
       </c>
       <c r="AB137" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC137" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC137" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -14878,11 +14876,11 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>28680462</v>
+        <v>28680490</v>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>MOESD Voices of Excellence</t>
+          <t>Modern Pillars of Excellence</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
@@ -14975,19 +14973,19 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>1811702</v>
+        <v>28680462</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Achievers of Excellence Club #1811702</t>
+          <t>MOESD Voices of Excellence</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -15001,17 +14999,17 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J139" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>-12</v>
-      </c>
-      <c r="L139" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L139" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M139" s="8" t="n">
@@ -15045,32 +15043,28 @@
       <c r="U139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V139" s="10" t="n">
-        <v>4</v>
+      <c r="V139" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X139" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z139" s="10" t="n">
-        <v>1</v>
+      <c r="Z139" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA139" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB139" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC139" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC139" s="4" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
@@ -15084,15 +15078,15 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>28680592</v>
+        <v>1811702</v>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>BBUC</t>
+          <t>Achievers of Excellence Club #1811702</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -15106,17 +15100,17 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L140" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L140" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M140" s="8" t="n">
@@ -15150,8 +15144,8 @@
       <c r="U140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V140" s="9" t="n">
-        <v>0</v>
+      <c r="V140" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W140" s="9" t="n">
         <v>0</v>
@@ -15162,16 +15156,20 @@
       <c r="Y140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z140" s="9" t="n">
-        <v>0</v>
+      <c r="Z140" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA140" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB140" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC140" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC140" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -15185,15 +15183,15 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>1200778</v>
+        <v>28680592</v>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Persuaders</t>
+          <t>BBUC</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -15207,17 +15205,17 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L141" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L141" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M141" s="8" t="n">
@@ -15234,7 +15232,7 @@
         </is>
       </c>
       <c r="P141" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q141" s="9" t="n">
         <v>0</v>
@@ -15245,38 +15243,34 @@
       <c r="S141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T141" s="10" t="n">
-        <v>1</v>
+      <c r="T141" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U141" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V141" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W141" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X141" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="10" t="n">
-        <v>1</v>
+      <c r="Z141" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA141" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB141" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC141" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC141" s="4" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
@@ -15290,15 +15284,15 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>7807079</v>
+        <v>1200778</v>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>San Salvador Explorers</t>
+          <t>Dynamic Persuaders</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -15312,13 +15306,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>-14</v>
+        <v>-7</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -15339,7 +15333,7 @@
         </is>
       </c>
       <c r="P142" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q142" s="9" t="n">
         <v>0</v>
@@ -15350,36 +15344,36 @@
       <c r="S142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T142" s="9" t="n">
-        <v>0</v>
+      <c r="T142" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U142" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V142" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W142" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X142" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z142" s="9" t="n">
-        <v>0</v>
+      <c r="Z142" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA142" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB142" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC142" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -15395,15 +15389,15 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>7548881</v>
+        <v>7807079</v>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Visionaries Toastmasters Club</t>
+          <t>San Salvador Explorers</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -15417,13 +15411,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -15444,16 +15438,16 @@
         </is>
       </c>
       <c r="P143" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q143" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R143" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S143" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T143" s="9" t="n">
         <v>0</v>
@@ -15462,49 +15456,49 @@
         <v>0</v>
       </c>
       <c r="V143" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W143" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X143" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z143" s="10" t="n">
-        <v>1</v>
+      <c r="Z143" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA143" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB143" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC143" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>63</t>
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>5183408</v>
+        <v>7548881</v>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>B.P.S.U. Excellers</t>
+          <t>Visionaries Toastmasters Club</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
@@ -15522,13 +15516,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J144" s="4" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -15536,11 +15530,11 @@
         </is>
       </c>
       <c r="M144" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N144" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O144" s="7" t="inlineStr">
@@ -15549,31 +15543,31 @@
         </is>
       </c>
       <c r="P144" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q144" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R144" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S144" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T144" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T144" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U144" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V144" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W144" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X144" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y144" s="9" t="n">
         <v>0</v>
@@ -15581,13 +15575,17 @@
       <c r="Z144" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA144" s="9" t="n">
-        <v>0</v>
+      <c r="AA144" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB144" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC144" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC144" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -15601,11 +15599,11 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>6847742</v>
+        <v>5183408</v>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>B.U.T. Abaco Trail Blazers</t>
+          <t>B.P.S.U. Excellers</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
@@ -15623,13 +15621,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J145" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
@@ -15637,11 +15635,11 @@
         </is>
       </c>
       <c r="M145" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N145" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O145" s="7" t="inlineStr">
@@ -15653,7 +15651,7 @@
         <v>0</v>
       </c>
       <c r="Q145" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R145" s="9" t="n">
         <v>0</v>
@@ -15668,25 +15666,25 @@
         <v>0</v>
       </c>
       <c r="V145" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W145" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X145" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z145" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB145" s="4" t="n">
         <v>5</v>
-      </c>
-      <c r="Y145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA145" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB145" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="AC145" s="4" t="inlineStr"/>
     </row>
@@ -15702,35 +15700,35 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>839960</v>
+        <v>6847742</v>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Club Destiny</t>
+          <t>B.U.T. Abaco Trail Blazers</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G146" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I146" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F146" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G146" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H146" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I146" s="4" t="n">
-        <v>10</v>
-      </c>
       <c r="J146" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
@@ -15754,7 +15752,7 @@
         <v>0</v>
       </c>
       <c r="Q146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R146" s="9" t="n">
         <v>0</v>
@@ -15765,35 +15763,31 @@
       <c r="T146" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U146" s="10" t="n">
-        <v>1</v>
+      <c r="U146" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V146" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W146" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X146" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z146" s="10" t="n">
-        <v>1</v>
+      <c r="Z146" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA146" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB146" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC146" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC146" s="4" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -15807,15 +15801,15 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>28676271</v>
+        <v>839960</v>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Diversified Network Speakers Club</t>
+          <t>Club Destiny</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -15829,13 +15823,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
@@ -15856,7 +15850,7 @@
         </is>
       </c>
       <c r="P147" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q147" s="9" t="n">
         <v>0</v>
@@ -15870,17 +15864,17 @@
       <c r="T147" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U147" s="9" t="n">
-        <v>0</v>
+      <c r="U147" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V147" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W147" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X147" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y147" s="9" t="n">
         <v>0</v>
@@ -15892,11 +15886,11 @@
         <v>1</v>
       </c>
       <c r="AB147" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC147" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -15912,15 +15906,15 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>1425</v>
+        <v>28676271</v>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Freeport Eagles</t>
+          <t>Diversified Network Speakers Club</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>10</v>
@@ -15934,13 +15928,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J148" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>-14</v>
+        <v>-11</v>
       </c>
       <c r="L148" s="7" t="inlineStr">
         <is>
@@ -15961,7 +15955,7 @@
         </is>
       </c>
       <c r="P148" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q148" s="9" t="n">
         <v>0</v>
@@ -15975,17 +15969,17 @@
       <c r="T148" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U148" s="10" t="n">
-        <v>1</v>
+      <c r="U148" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V148" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W148" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X148" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y148" s="9" t="n">
         <v>0</v>
@@ -15997,11 +15991,11 @@
         <v>1</v>
       </c>
       <c r="AB148" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC148" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -16017,15 +16011,15 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>28676498</v>
+        <v>1425</v>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Rocky Shores Trending Orators</t>
+          <t>Freeport Eagles</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>10</v>
@@ -16039,13 +16033,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>-17</v>
+        <v>-13</v>
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
@@ -16066,7 +16060,7 @@
         </is>
       </c>
       <c r="P149" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q149" s="9" t="n">
         <v>0</v>
@@ -16077,36 +16071,36 @@
       <c r="S149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T149" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U149" s="9" t="n">
-        <v>0</v>
+      <c r="T149" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U149" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V149" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W149" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X149" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z149" s="9" t="n">
-        <v>0</v>
+      <c r="Z149" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA149" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB149" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC149" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -16118,19 +16112,19 @@
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>1360933</v>
+        <v>28676498</v>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>B.P.S.U. Majestic Marlins Toastmasters Club</t>
+          <t>Rocky Shores Trending Orators</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -16144,13 +16138,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="J150" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>-8</v>
+        <v>-16</v>
       </c>
       <c r="L150" s="7" t="inlineStr">
         <is>
@@ -16171,47 +16165,47 @@
         </is>
       </c>
       <c r="P150" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q150" s="10" t="n">
         <v>2</v>
       </c>
+      <c r="Q150" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="R150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S150" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T150" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U150" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V150" s="10" t="n">
+      <c r="S150" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T150" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U150" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V150" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W150" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X150" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W150" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X150" s="10" t="n">
-        <v>6</v>
-      </c>
       <c r="Y150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z150" s="10" t="n">
-        <v>1</v>
+      <c r="Z150" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA150" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB150" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC150" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -16227,15 +16221,15 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>28677257</v>
+        <v>1360933</v>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Bethel Toastmasters Club</t>
+          <t>B.P.S.U. Majestic Marlins Toastmasters Club</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -16249,13 +16243,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>-15</v>
+        <v>-8</v>
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
@@ -16278,29 +16272,29 @@
       <c r="P151" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q151" s="9" t="n">
-        <v>0</v>
+      <c r="Q151" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S151" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T151" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U151" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V151" s="9" t="n">
-        <v>0</v>
+      <c r="S151" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T151" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U151" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V151" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W151" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X151" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y151" s="9" t="n">
         <v>0</v>
@@ -16332,11 +16326,11 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>5922881</v>
+        <v>28677257</v>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>BFM Diplomats</t>
+          <t>Bethel Toastmasters Club</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">
@@ -16357,10 +16351,10 @@
         <v>10</v>
       </c>
       <c r="J152" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="L152" s="7" t="inlineStr">
         <is>
@@ -16381,7 +16375,7 @@
         </is>
       </c>
       <c r="P152" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q152" s="9" t="n">
         <v>0</v>
@@ -16405,7 +16399,7 @@
         <v>0</v>
       </c>
       <c r="X152" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y152" s="9" t="n">
         <v>0</v>
@@ -16417,11 +16411,11 @@
         <v>1</v>
       </c>
       <c r="AB152" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC152" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -16437,15 +16431,15 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>6724527</v>
+        <v>5922881</v>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Club Carmichael</t>
+          <t>BFM Diplomats</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F153" s="6" t="n">
         <v>10</v>
@@ -16459,72 +16453,76 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J153" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K153" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L153" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M153" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N153" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O153" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X153" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z153" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA153" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB153" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="K153" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L153" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M153" s="8" t="n">
-        <v>46387</v>
-      </c>
-      <c r="N153" s="4" t="inlineStr">
-        <is>
-          <t>Officer list on time</t>
-        </is>
-      </c>
-      <c r="O153" s="7" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V153" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB153" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC153" s="4" t="inlineStr"/>
+      <c r="AC153" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
@@ -16538,98 +16536,94 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>7108</v>
+        <v>6724527</v>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Ernest T. Strachan Advanced</t>
+          <t>Club Carmichael</t>
         </is>
       </c>
       <c r="E154" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G154" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I154" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J154" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K154" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L154" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M154" s="8" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N154" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O154" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V154" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB154" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F154" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G154" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H154" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I154" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="J154" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="K154" s="4" t="n">
-        <v>-15</v>
-      </c>
-      <c r="L154" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M154" s="8" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N154" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O154" s="7" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P154" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q154" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R154" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S154" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T154" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U154" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V154" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W154" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X154" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y154" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z154" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA154" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB154" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC154" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+      <c r="AC154" s="4" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -16639,19 +16633,19 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>71</t>
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>7842684</v>
+        <v>7108</v>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>ABC Ambassadors</t>
+          <t>Ernest T. Strachan Advanced</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>10</v>
@@ -16665,13 +16659,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J155" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>-5</v>
+        <v>-13</v>
       </c>
       <c r="L155" s="7" t="inlineStr">
         <is>
@@ -16679,11 +16673,11 @@
         </is>
       </c>
       <c r="M155" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N155" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O155" s="7" t="inlineStr">
@@ -16692,28 +16686,28 @@
         </is>
       </c>
       <c r="P155" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q155" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q155" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R155" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S155" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T155" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U155" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T155" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U155" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V155" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X155" s="10" t="n">
         <v>7</v>
@@ -16721,11 +16715,11 @@
       <c r="Y155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z155" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA155" s="9" t="n">
-        <v>0</v>
+      <c r="Z155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA155" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB155" s="4" t="n">
         <v>9</v>
@@ -16748,15 +16742,15 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>6484905</v>
+        <v>7842684</v>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>AGOC Nationbuilders</t>
+          <t>ABC Ambassadors</t>
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -16770,13 +16764,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J156" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="L156" s="7" t="inlineStr">
         <is>
@@ -16784,11 +16778,11 @@
         </is>
       </c>
       <c r="M156" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N156" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O156" s="7" t="inlineStr">
@@ -16799,29 +16793,29 @@
       <c r="P156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" s="10" t="n">
-        <v>2</v>
+      <c r="Q156" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R156" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S156" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T156" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U156" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T156" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U156" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V156" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W156" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X156" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y156" s="9" t="n">
         <v>0</v>
@@ -16829,15 +16823,15 @@
       <c r="Z156" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA156" s="10" t="n">
-        <v>1</v>
+      <c r="AA156" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB156" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC156" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -16853,15 +16847,15 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>1050379</v>
+        <v>6484905</v>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>E.T. Communicators</t>
+          <t>AGOC Nationbuilders</t>
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -16875,13 +16869,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J157" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
@@ -16908,25 +16902,25 @@
         <v>2</v>
       </c>
       <c r="R157" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S157" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="S157" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="T157" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U157" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V157" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="V157" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="W157" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X157" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y157" s="9" t="n">
         <v>0</v>
@@ -16938,11 +16932,11 @@
         <v>1</v>
       </c>
       <c r="AB157" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC157" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -16958,15 +16952,15 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>7775252</v>
+        <v>1050379</v>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>The First Breakfast Toastmasters Club of The Bahamas</t>
+          <t>E.T. Communicators</t>
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F158" s="6" t="n">
         <v>10</v>
@@ -16980,13 +16974,13 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="L158" s="7" t="inlineStr">
         <is>
@@ -17007,31 +17001,31 @@
         </is>
       </c>
       <c r="P158" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q158" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q158" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R158" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S158" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="S158" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="T158" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U158" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V158" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W158" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X158" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y158" s="9" t="n">
         <v>0</v>
@@ -17059,19 +17053,19 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>72</t>
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>6742900</v>
+        <v>7775252</v>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>B.U.T. North Eleuthera Shakers</t>
+          <t>The First Breakfast Toastmasters Club of The Bahamas</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>10</v>
@@ -17085,13 +17079,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>-8</v>
+        <v>-13</v>
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
@@ -17112,10 +17106,10 @@
         </is>
       </c>
       <c r="P159" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q159" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R159" s="9" t="n">
         <v>0</v>
@@ -17129,14 +17123,14 @@
       <c r="U159" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V159" s="10" t="n">
-        <v>4</v>
+      <c r="V159" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W159" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X159" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y159" s="9" t="n">
         <v>0</v>
@@ -17168,15 +17162,15 @@
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>7012965</v>
+        <v>6742900</v>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Eloquent Voices</t>
+          <t>B.U.T. North Eleuthera Shakers</t>
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -17190,13 +17184,13 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J160" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="L160" s="7" t="inlineStr">
         <is>
@@ -17220,7 +17214,7 @@
         <v>0</v>
       </c>
       <c r="Q160" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R160" s="9" t="n">
         <v>0</v>
@@ -17228,17 +17222,17 @@
       <c r="S160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T160" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U160" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V160" s="9" t="n">
-        <v>0</v>
+      <c r="T160" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U160" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V160" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W160" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X160" s="10" t="n">
         <v>6</v>
@@ -17253,11 +17247,11 @@
         <v>1</v>
       </c>
       <c r="AB160" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC160" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -17273,15 +17267,15 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>1600</v>
+        <v>7012965</v>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>First Bahamas Branch of Toastmasters</t>
+          <t>Eloquent Voices</t>
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F161" s="6" t="n">
         <v>10</v>
@@ -17295,17 +17289,17 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="J161" s="4" t="n">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L161" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L161" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M161" s="8" t="n">
@@ -17321,32 +17315,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P161" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q161" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R161" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="S161" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T161" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U161" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V161" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W161" s="10" t="n">
-        <v>15</v>
+      <c r="P161" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q161" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T161" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U161" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V161" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W161" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X161" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y161" s="9" t="n">
         <v>0</v>
@@ -17358,11 +17352,11 @@
         <v>1</v>
       </c>
       <c r="AB161" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC161" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -17378,15 +17372,15 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>1513325</v>
+        <v>1600</v>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Pinnacle Seekers</t>
+          <t>First Bahamas Branch of Toastmasters</t>
         </is>
       </c>
       <c r="E162" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F162" s="6" t="n">
         <v>10</v>
@@ -17400,25 +17394,25 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="J162" s="4" t="n">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L162" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>9</v>
+      </c>
+      <c r="L162" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M162" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N162" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O162" s="7" t="inlineStr">
@@ -17426,32 +17420,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P162" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q162" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R162" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S162" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T162" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U162" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V162" s="9" t="n">
+      <c r="P162" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q162" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="W162" s="9" t="n">
-        <v>0</v>
+      <c r="R162" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S162" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T162" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U162" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V162" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W162" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="X162" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y162" s="9" t="n">
         <v>0</v>
@@ -17459,35 +17453,35 @@
       <c r="Z162" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA162" s="9" t="n">
-        <v>0</v>
+      <c r="AA162" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB162" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC162" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>73</t>
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>2449</v>
+        <v>1513325</v>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Bradenton Toastmasters Club</t>
+          <t>Pinnacle Seekers</t>
         </is>
       </c>
       <c r="E163" s="5" t="n">
@@ -17505,13 +17499,13 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J163" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L163" s="7" t="inlineStr">
         <is>
@@ -17550,13 +17544,13 @@
         <v>0</v>
       </c>
       <c r="V163" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X163" s="9" t="n">
-        <v>3</v>
+      <c r="X163" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y163" s="9" t="n">
         <v>0</v>
@@ -17567,8 +17561,14 @@
       <c r="AA163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AB163" s="4" t="n"/>
-      <c r="AC163" s="4" t="inlineStr"/>
+      <c r="AB163" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC163" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
@@ -17582,89 +17582,89 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>7719</v>
+        <v>2449</v>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>FCCI Toastmasters Club</t>
+          <t>Bradenton Toastmasters Club</t>
         </is>
       </c>
       <c r="E164" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G164" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I164" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J164" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="K164" s="4" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L164" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M164" s="8" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N164" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O164" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P164" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q164" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T164" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U164" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V164" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W164" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X164" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F164" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G164" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H164" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I164" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="J164" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="K164" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L164" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M164" s="8" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N164" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O164" s="7" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P164" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q164" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R164" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S164" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T164" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U164" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V164" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W164" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X164" s="10" t="n">
-        <v>6</v>
-      </c>
       <c r="Y164" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Z164" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA164" s="10" t="n">
-        <v>1</v>
+      <c r="AA164" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB164" s="4" t="n"/>
       <c r="AC164" s="4" t="inlineStr"/>
@@ -17681,15 +17681,15 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>9352</v>
+        <v>7719</v>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Positively Speaking Toastmasters Club</t>
+          <t>FCCI Toastmasters Club</t>
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F165" s="6" t="n">
         <v>10</v>
@@ -17703,17 +17703,17 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="J165" s="4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L165" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-6</v>
+      </c>
+      <c r="L165" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M165" s="8" t="n">
@@ -17730,7 +17730,7 @@
         </is>
       </c>
       <c r="P165" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q165" s="9" t="n">
         <v>0</v>
@@ -17738,23 +17738,23 @@
       <c r="R165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S165" s="9" t="n">
-        <v>0</v>
+      <c r="S165" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T165" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U165" s="9" t="n">
-        <v>0</v>
+      <c r="U165" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V165" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W165" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X165" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y165" s="9" t="n">
         <v>0</v>
@@ -17780,15 +17780,15 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>1197988</v>
+        <v>9352</v>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Power Speakers of MCG</t>
+          <t>Positively Speaking Toastmasters Club</t>
         </is>
       </c>
       <c r="E166" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F166" s="6" t="n">
         <v>10</v>
@@ -17802,13 +17802,13 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J166" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L166" s="7" t="inlineStr">
         <is>
@@ -17816,11 +17816,11 @@
         </is>
       </c>
       <c r="M166" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N166" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O166" s="7" t="inlineStr">
@@ -17840,29 +17840,29 @@
       <c r="S166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T166" s="9" t="n">
-        <v>0</v>
+      <c r="T166" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U166" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V166" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X166" s="9" t="n">
-        <v>0</v>
+      <c r="X166" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z166" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA166" s="9" t="n">
-        <v>0</v>
+      <c r="Z166" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA166" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB166" s="4" t="n"/>
       <c r="AC166" s="4" t="inlineStr"/>
@@ -17879,15 +17879,15 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>7912158</v>
+        <v>1197988</v>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>TTEC-WIL Toastmasters</t>
+          <t>Power Speakers of MCG</t>
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>10</v>
@@ -17901,17 +17901,17 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J167" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L167" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L167" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M167" s="8" t="n">
@@ -17945,11 +17945,11 @@
       <c r="U167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V167" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W167" s="10" t="n">
-        <v>13</v>
+      <c r="V167" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W167" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X167" s="9" t="n">
         <v>0</v>
@@ -17957,8 +17957,8 @@
       <c r="Y167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z167" s="10" t="n">
-        <v>1</v>
+      <c r="Z167" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA167" s="9" t="n">
         <v>0</v>
@@ -17974,15 +17974,15 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>6026</v>
+        <v>7912158</v>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Sarasota Evening Club</t>
+          <t>TTEC-WIL Toastmasters</t>
         </is>
       </c>
       <c r="E168" s="5" t="n">
@@ -18000,13 +18000,13 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J168" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
@@ -18014,11 +18014,11 @@
         </is>
       </c>
       <c r="M168" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N168" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O168" s="7" t="inlineStr">
@@ -18030,13 +18030,13 @@
         <v>0</v>
       </c>
       <c r="Q168" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R168" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S168" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T168" s="9" t="n">
         <v>0</v>
@@ -18047,11 +18047,11 @@
       <c r="V168" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W168" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="X168" s="10" t="n">
-        <v>4</v>
+      <c r="W168" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="X168" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y168" s="9" t="n">
         <v>0</v>
@@ -18059,8 +18059,8 @@
       <c r="Z168" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA168" s="10" t="n">
-        <v>1</v>
+      <c r="AA168" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB168" s="4" t="n"/>
       <c r="AC168" s="4" t="inlineStr"/>
@@ -18077,11 +18077,11 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>777513</v>
+        <v>6026</v>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Sarasota Speakers Exchange Toastmasters Club</t>
+          <t>Sarasota Evening Club</t>
         </is>
       </c>
       <c r="E169" s="5" t="n">
@@ -18099,17 +18099,17 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J169" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="J169" s="4" t="n">
-        <v>17</v>
-      </c>
       <c r="K169" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L169" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L169" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M169" s="8" t="n">
@@ -18126,16 +18126,16 @@
         </is>
       </c>
       <c r="P169" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q169" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R169" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S169" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T169" s="9" t="n">
         <v>0</v>
@@ -18147,10 +18147,10 @@
         <v>4</v>
       </c>
       <c r="W169" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="X169" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="X169" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y169" s="9" t="n">
         <v>0</v>
@@ -18176,11 +18176,11 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>1958</v>
+        <v>777513</v>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Sarasota Toastmasters Club</t>
+          <t>Sarasota Speakers Exchange Toastmasters Club</t>
         </is>
       </c>
       <c r="E170" s="5" t="n">
@@ -18198,17 +18198,17 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J170" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="K170" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L170" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L170" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M170" s="8" t="n">
@@ -18228,7 +18228,7 @@
         <v>1</v>
       </c>
       <c r="Q170" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R170" s="9" t="n">
         <v>0</v>
@@ -18246,10 +18246,10 @@
         <v>4</v>
       </c>
       <c r="W170" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X170" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y170" s="9" t="n">
         <v>0</v>
@@ -18275,15 +18275,15 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>7327</v>
+        <v>1958</v>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Sarasota WCR Toastmasters Club</t>
+          <t>Sarasota Toastmasters Club</t>
         </is>
       </c>
       <c r="E171" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F171" s="6" t="n">
         <v>10</v>
@@ -18297,17 +18297,17 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J171" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L171" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L171" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M171" s="8" t="n">
@@ -18327,7 +18327,7 @@
         <v>1</v>
       </c>
       <c r="Q171" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R171" s="9" t="n">
         <v>0</v>
@@ -18341,14 +18341,14 @@
       <c r="U171" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V171" s="9" t="n">
-        <v>1</v>
+      <c r="V171" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W171" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X171" s="10" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="X171" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y171" s="9" t="n">
         <v>0</v>
@@ -18370,15 +18370,15 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>6485018</v>
+        <v>7327</v>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>CC Gov Toastmasters</t>
+          <t>Sarasota WCR Toastmasters Club</t>
         </is>
       </c>
       <c r="E172" s="5" t="n">
@@ -18396,13 +18396,13 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J172" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         </is>
       </c>
       <c r="P172" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q172" s="9" t="n">
         <v>0</v>
@@ -18446,8 +18446,8 @@
       <c r="W172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X172" s="9" t="n">
-        <v>0</v>
+      <c r="X172" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y172" s="9" t="n">
         <v>0</v>
@@ -18473,15 +18473,15 @@
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>28677961</v>
+        <v>6485018</v>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>ECCA Toastmasters</t>
+          <t>CC Gov Toastmasters</t>
         </is>
       </c>
       <c r="E173" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F173" s="6" t="n">
         <v>10</v>
@@ -18495,25 +18495,25 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J173" s="4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L173" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-3</v>
+      </c>
+      <c r="L173" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M173" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N173" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O173" s="7" t="inlineStr">
@@ -18540,7 +18540,7 @@
         <v>0</v>
       </c>
       <c r="V173" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W173" s="9" t="n">
         <v>0</v>
@@ -18551,11 +18551,11 @@
       <c r="Y173" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z173" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA173" s="9" t="n">
-        <v>0</v>
+      <c r="Z173" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA173" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB173" s="4" t="n"/>
       <c r="AC173" s="4" t="inlineStr"/>
@@ -18572,15 +18572,15 @@
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>1395623</v>
+        <v>28677961</v>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>North Port Toastmasters</t>
+          <t>ECCA Toastmasters</t>
         </is>
       </c>
       <c r="E174" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F174" s="6" t="n">
         <v>10</v>
@@ -18594,13 +18594,13 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J174" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L174" s="7" t="inlineStr">
         <is>
@@ -18608,11 +18608,11 @@
         </is>
       </c>
       <c r="M174" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N174" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O174" s="7" t="inlineStr">
@@ -18624,7 +18624,7 @@
         <v>0</v>
       </c>
       <c r="Q174" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R174" s="9" t="n">
         <v>0</v>
@@ -18639,22 +18639,22 @@
         <v>0</v>
       </c>
       <c r="V174" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W174" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X174" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y174" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z174" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA174" s="10" t="n">
-        <v>1</v>
+      <c r="Z174" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA174" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB174" s="4" t="n"/>
       <c r="AC174" s="4" t="inlineStr"/>
@@ -18671,15 +18671,15 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>28679881</v>
+        <v>1395623</v>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters North Port EDD</t>
+          <t>North Port Toastmasters</t>
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F175" s="6" t="n">
         <v>10</v>
@@ -18693,13 +18693,13 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J175" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="L175" s="7" t="inlineStr">
         <is>
@@ -18707,11 +18707,11 @@
         </is>
       </c>
       <c r="M175" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N175" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O175" s="7" t="inlineStr">
@@ -18720,10 +18720,10 @@
         </is>
       </c>
       <c r="P175" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q175" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R175" s="9" t="n">
         <v>0</v>
@@ -18752,8 +18752,8 @@
       <c r="Z175" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA175" s="9" t="n">
-        <v>0</v>
+      <c r="AA175" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB175" s="4" t="n"/>
       <c r="AC175" s="4" t="inlineStr"/>
@@ -18770,80 +18770,80 @@
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>5486</v>
+        <v>28679881</v>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Venice Area Toastmasters Club</t>
+          <t>Toastmasters North Port EDD</t>
         </is>
       </c>
       <c r="E176" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F176" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G176" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H176" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I176" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J176" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K176" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L176" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M176" s="8" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N176" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O176" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P176" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q176" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R176" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S176" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T176" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U176" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V176" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F176" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G176" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H176" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I176" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="J176" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="K176" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L176" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M176" s="8" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N176" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O176" s="7" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P176" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q176" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R176" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S176" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T176" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U176" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V176" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="W176" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X176" s="10" t="n">
-        <v>4</v>
+      <c r="X176" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y176" s="9" t="n">
         <v>0</v>
@@ -18851,8 +18851,8 @@
       <c r="Z176" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA176" s="10" t="n">
-        <v>1</v>
+      <c r="AA176" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB176" s="4" t="n"/>
       <c r="AC176" s="4" t="inlineStr"/>
@@ -18865,15 +18865,15 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>82</t>
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>9051</v>
+        <v>5486</v>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Cape Coral Toastmasters Club</t>
+          <t>Venice Area Toastmasters Club</t>
         </is>
       </c>
       <c r="E177" s="5" t="n">
@@ -18891,17 +18891,17 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="J177" s="4" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K177" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="L177" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L177" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M177" s="8" t="n">
@@ -18927,7 +18927,7 @@
         <v>0</v>
       </c>
       <c r="S177" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T177" s="10" t="n">
         <v>1</v>
@@ -18936,7 +18936,7 @@
         <v>0</v>
       </c>
       <c r="V177" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W177" s="9" t="n">
         <v>0</v>
@@ -18968,15 +18968,15 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>5701</v>
+        <v>9051</v>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Electric Toasters Club</t>
+          <t>Cape Coral Toastmasters Club</t>
         </is>
       </c>
       <c r="E178" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F178" s="6" t="n">
         <v>10</v>
@@ -18990,17 +18990,17 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J178" s="4" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L178" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L178" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M178" s="8" t="n">
@@ -19026,7 +19026,7 @@
         <v>0</v>
       </c>
       <c r="S178" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T178" s="10" t="n">
         <v>1</v>
@@ -19034,14 +19034,14 @@
       <c r="U178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V178" s="10" t="n">
+      <c r="V178" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W178" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X178" s="10" t="n">
         <v>4</v>
-      </c>
-      <c r="W178" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X178" s="10" t="n">
-        <v>6</v>
       </c>
       <c r="Y178" s="9" t="n">
         <v>0</v>
@@ -19067,15 +19067,15 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>1702</v>
+        <v>5701</v>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Ft Myers Toastmasters Club # 1702</t>
+          <t>Electric Toasters Club</t>
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F179" s="6" t="n">
         <v>10</v>
@@ -19089,13 +19089,13 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J179" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L179" s="4" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>1</v>
       </c>
       <c r="Q179" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R179" s="9" t="n">
         <v>0</v>
@@ -19130,17 +19130,17 @@
       <c r="T179" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U179" s="10" t="n">
-        <v>1</v>
+      <c r="U179" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V179" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W179" s="10" t="n">
-        <v>5</v>
+      <c r="W179" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="X179" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y179" s="9" t="n">
         <v>0</v>
@@ -19166,15 +19166,15 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>28679126</v>
+        <v>1702</v>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Greater Fort Myers Chamber of Commerce Toastmasters Club</t>
+          <t>Ft Myers Toastmasters Club # 1702</t>
         </is>
       </c>
       <c r="E180" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F180" s="6" t="n">
         <v>10</v>
@@ -19188,17 +19188,17 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J180" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L180" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L180" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M180" s="8" t="n">
@@ -19215,10 +19215,10 @@
         </is>
       </c>
       <c r="P180" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q180" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R180" s="9" t="n">
         <v>0</v>
@@ -19226,20 +19226,20 @@
       <c r="S180" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T180" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U180" s="9" t="n">
-        <v>0</v>
+      <c r="T180" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U180" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V180" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W180" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X180" s="9" t="n">
-        <v>3</v>
+      <c r="W180" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="X180" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y180" s="9" t="n">
         <v>0</v>
@@ -19261,19 +19261,19 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>6743270</v>
+        <v>28679126</v>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Avow</t>
+          <t>Greater Fort Myers Chamber of Commerce Toastmasters Club</t>
         </is>
       </c>
       <c r="E181" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F181" s="6" t="n">
         <v>10</v>
@@ -19287,13 +19287,13 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J181" s="4" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K181" s="4" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="L181" s="7" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         </is>
       </c>
       <c r="P181" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q181" s="9" t="n">
         <v>0</v>
@@ -19331,14 +19331,14 @@
       <c r="U181" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V181" s="9" t="n">
-        <v>2</v>
+      <c r="V181" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W181" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X181" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y181" s="9" t="n">
         <v>0</v>
@@ -19364,11 +19364,11 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>8838</v>
+        <v>6743270</v>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Naples Advanced Toastmasters</t>
+          <t>Avow</t>
         </is>
       </c>
       <c r="E182" s="5" t="n">
@@ -19386,13 +19386,13 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J182" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>-10</v>
+        <v>-1</v>
       </c>
       <c r="L182" s="7" t="inlineStr">
         <is>
@@ -19431,13 +19431,13 @@
         <v>0</v>
       </c>
       <c r="V182" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W182" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X182" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y182" s="9" t="n">
         <v>0</v>
@@ -19463,15 +19463,15 @@
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>9628</v>
+        <v>8838</v>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Naples Sunrise Bay Toastmasters Club</t>
+          <t>Naples Advanced Toastmasters</t>
         </is>
       </c>
       <c r="E183" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F183" s="6" t="n">
         <v>10</v>
@@ -19485,17 +19485,17 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="J183" s="4" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="K183" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L183" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L183" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M183" s="8" t="n">
@@ -19512,31 +19512,31 @@
         </is>
       </c>
       <c r="P183" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q183" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R183" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S183" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T183" s="10" t="n">
-        <v>1</v>
+      <c r="S183" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T183" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U183" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V183" s="10" t="n">
-        <v>4</v>
+      <c r="V183" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W183" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="X183" s="10" t="n">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="X183" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y183" s="9" t="n">
         <v>0</v>
@@ -19562,15 +19562,15 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>2835</v>
+        <v>9628</v>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Naples Toastmasters Club</t>
+          <t>Naples Sunrise Bay Toastmasters Club</t>
         </is>
       </c>
       <c r="E184" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F184" s="6" t="n">
         <v>10</v>
@@ -19584,13 +19584,13 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="J184" s="4" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="L184" s="4" t="inlineStr">
         <is>
@@ -19611,19 +19611,19 @@
         </is>
       </c>
       <c r="P184" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q184" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R184" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S184" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T184" s="9" t="n">
-        <v>0</v>
+      <c r="S184" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T184" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U184" s="9" t="n">
         <v>0</v>
@@ -19631,11 +19631,11 @@
       <c r="V184" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W184" s="10" t="n">
+      <c r="W184" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="X184" s="10" t="n">
         <v>5</v>
-      </c>
-      <c r="X184" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="Y184" s="9" t="n">
         <v>0</v>
@@ -19649,8 +19649,107 @@
       <c r="AB184" s="4" t="n"/>
       <c r="AC184" s="4" t="inlineStr"/>
     </row>
+    <row r="185">
+      <c r="A185" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="n">
+        <v>2835</v>
+      </c>
+      <c r="D185" s="4" t="inlineStr">
+        <is>
+          <t>Naples Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F185" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G185" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H185" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I185" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J185" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="K185" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L185" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M185" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N185" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O185" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P185" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q185" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R185" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S185" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T185" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U185" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V185" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W185" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="X185" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y185" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z185" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA185" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB185" s="4" t="n"/>
+      <c r="AC185" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC184"/>
+  <autoFilter ref="A1:AC185"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19836,7 +19935,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -19968,7 +20067,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -20082,7 +20181,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -20100,7 +20199,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -20265,7 +20364,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -20361,13 +20460,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>3.4</v>
+        <v>3.17</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
         <v>4</v>
@@ -20379,7 +20478,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -20397,7 +20496,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -20430,7 +20529,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
@@ -20529,7 +20628,7 @@
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>3.17</v>
+        <v>3.5</v>
       </c>
       <c r="E26" t="n">
         <v>2</v>
@@ -20577,7 +20676,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -20760,7 +20859,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -20808,7 +20907,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -20826,7 +20925,7 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>

--- a/docs/d/47/inyear.xlsx
+++ b/docs/d/47/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 21 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 21 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 30 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 30 clubs short</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="P4" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" s="9" t="n">
         <v>1</v>
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>0</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" s="9" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="P6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="9" t="n">
         <v>0</v>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="P9" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q9" s="10" t="n">
         <v>2</v>
@@ -1622,8 +1622,8 @@
       <c r="T9" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U9" s="9" t="n">
-        <v>0</v>
+      <c r="U9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V9" s="10" t="n">
         <v>4</v>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1686,13 +1686,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -1712,8 +1712,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P10" s="9" t="n">
-        <v>3</v>
+      <c r="P10" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q10" s="10" t="n">
         <v>2</v>
@@ -1734,7 +1734,7 @@
         <v>4</v>
       </c>
       <c r="W10" s="10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X10" s="10" t="n">
         <v>7</v>
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
@@ -2292,13 +2292,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W16" s="9" t="n">
         <v>0</v>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2626,7 +2626,7 @@
         </is>
       </c>
       <c r="P19" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="9" t="n">
         <v>0</v>
@@ -2637,8 +2637,8 @@
       <c r="S19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T19" s="9" t="n">
-        <v>0</v>
+      <c r="T19" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U19" s="9" t="n">
         <v>0</v>
@@ -2906,13 +2906,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>4</v>
       </c>
       <c r="W22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" s="10" t="n">
         <v>6</v>
@@ -3102,7 +3102,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3142,8 +3142,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P24" s="9" t="n">
-        <v>3</v>
+      <c r="P24" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q24" s="9" t="n">
         <v>0</v>
@@ -3157,8 +3157,8 @@
       <c r="T24" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U24" s="9" t="n">
-        <v>0</v>
+      <c r="U24" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V24" s="9" t="n">
         <v>3</v>
@@ -3221,13 +3221,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>2</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" s="9" t="n">
         <v>0</v>
@@ -3870,10 +3870,10 @@
         </is>
       </c>
       <c r="P31" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" s="9" t="n">
         <v>0</v>
@@ -4249,13 +4249,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-19</v>
+        <v>-6</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4350,13 +4350,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4455,13 +4455,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4661,13 +4661,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>61</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>4</v>
       </c>
       <c r="W39" s="10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X39" s="10" t="n">
         <v>6</v>
@@ -5586,13 +5586,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5788,13 +5788,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -5893,13 +5893,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="W51" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X51" s="10" t="n">
         <v>7</v>
@@ -6126,7 +6126,7 @@
         </is>
       </c>
       <c r="P53" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q53" s="9" t="n">
         <v>1</v>
@@ -6440,7 +6440,7 @@
         <v>1</v>
       </c>
       <c r="Q56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" s="9" t="n">
         <v>0</v>
@@ -6620,13 +6620,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6725,13 +6725,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>4</v>
       </c>
       <c r="W59" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X59" s="10" t="n">
         <v>4</v>
@@ -7242,13 +7242,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -8179,13 +8179,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -8589,13 +8589,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
@@ -8694,13 +8694,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>4</v>
       </c>
       <c r="W78" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X78" s="10" t="n">
         <v>7</v>
@@ -8799,13 +8799,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>4</v>
       </c>
       <c r="W79" s="10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X79" s="10" t="n">
         <v>5</v>
@@ -9461,7 +9461,7 @@
         <v>0</v>
       </c>
       <c r="S85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T85" s="10" t="n">
         <v>1</v>
@@ -9631,13 +9631,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>-24</v>
+        <v>-23</v>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10976,13 +10976,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>52</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
@@ -11005,8 +11005,8 @@
       <c r="P100" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q100" s="9" t="n">
-        <v>1</v>
+      <c r="Q100" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R100" s="9" t="n">
         <v>0</v>
@@ -11024,7 +11024,7 @@
         <v>4</v>
       </c>
       <c r="W100" s="10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="X100" s="10" t="n">
         <v>4</v>
@@ -11081,13 +11081,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
@@ -11396,13 +11396,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>4</v>
       </c>
       <c r="W104" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X104" s="10" t="n">
         <v>4</v>
@@ -11705,13 +11705,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>4</v>
       </c>
       <c r="W107" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X107" s="10" t="n">
         <v>7</v>
@@ -12039,7 +12039,7 @@
         </is>
       </c>
       <c r="P110" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q110" s="9" t="n">
         <v>1</v>
@@ -12241,7 +12241,7 @@
         </is>
       </c>
       <c r="P112" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q112" s="9" t="n">
         <v>0</v>
@@ -12521,13 +12521,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>4</v>
       </c>
       <c r="W115" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X115" s="10" t="n">
         <v>5</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13551,13 +13551,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>-16</v>
+        <v>-13</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -13586,8 +13586,8 @@
       <c r="R125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S125" s="9" t="n">
-        <v>1</v>
+      <c r="S125" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T125" s="9" t="n">
         <v>0</v>
@@ -13656,13 +13656,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -13701,7 +13701,7 @@
         <v>0</v>
       </c>
       <c r="V126" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W126" s="9" t="n">
         <v>0</v>
@@ -13846,7 +13846,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13898,8 +13898,8 @@
       <c r="S128" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T128" s="9" t="n">
-        <v>0</v>
+      <c r="T128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U128" s="9" t="n">
         <v>0</v>
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -14167,13 +14167,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
@@ -14214,8 +14214,8 @@
       <c r="V131" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W131" s="9" t="n">
-        <v>2</v>
+      <c r="W131" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X131" s="10" t="n">
         <v>7</v>
@@ -14299,7 +14299,7 @@
         </is>
       </c>
       <c r="P132" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q132" s="10" t="n">
         <v>2</v>
@@ -14377,13 +14377,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         </is>
       </c>
       <c r="P135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q135" s="9" t="n">
         <v>1</v>
@@ -14692,13 +14692,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -15411,13 +15411,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -15662,8 +15662,8 @@
       <c r="T145" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U145" s="9" t="n">
-        <v>0</v>
+      <c r="U145" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V145" s="9" t="n">
         <v>1</v>
@@ -15722,13 +15722,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
@@ -15823,13 +15823,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>1</v>
       </c>
       <c r="V147" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W147" s="9" t="n">
         <v>0</v>
@@ -15928,13 +15928,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L148" s="7" t="inlineStr">
         <is>
@@ -16659,13 +16659,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L155" s="7" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         </is>
       </c>
       <c r="P158" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q158" s="10" t="n">
         <v>2</v>
@@ -17436,7 +17436,7 @@
         <v>1</v>
       </c>
       <c r="U162" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V162" s="10" t="n">
         <v>4</v>
@@ -17604,13 +17604,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L164" s="7" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         </is>
       </c>
       <c r="E170" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F170" s="6" t="n">
         <v>10</v>
@@ -18198,13 +18198,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
@@ -18245,8 +18245,8 @@
       <c r="V170" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W170" s="9" t="n">
-        <v>3</v>
+      <c r="W170" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X170" s="9" t="n">
         <v>0</v>
@@ -18679,7 +18679,7 @@
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F175" s="6" t="n">
         <v>10</v>
@@ -18693,13 +18693,13 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L175" s="7" t="inlineStr">
         <is>
@@ -18728,8 +18728,8 @@
       <c r="R175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S175" s="9" t="n">
-        <v>0</v>
+      <c r="S175" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T175" s="9" t="n">
         <v>0</v>
@@ -18819,7 +18819,7 @@
         </is>
       </c>
       <c r="P176" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q176" s="9" t="n">
         <v>0</v>
@@ -19570,7 +19570,7 @@
         </is>
       </c>
       <c r="E184" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F184" s="6" t="n">
         <v>10</v>
@@ -19611,13 +19611,13 @@
         </is>
       </c>
       <c r="P184" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q184" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Q184" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R184" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S184" s="10" t="n">
         <v>4</v>
@@ -19869,7 +19869,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -19935,7 +19935,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -19968,7 +19968,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -20463,7 +20463,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>3.17</v>
+        <v>3.33</v>
       </c>
       <c r="E21" t="n">
         <v>2</v>
@@ -20595,7 +20595,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -20628,13 +20628,13 @@
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>3.5</v>
+        <v>3.83</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -20727,7 +20727,7 @@
         <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -20892,7 +20892,7 @@
         <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -20925,7 +20925,7 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -20991,13 +20991,13 @@
         <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
